--- a/Interim3/ENME473_Q7_BoxDimensions.xlsx
+++ b/Interim3/ENME473_Q7_BoxDimensions.xlsx
@@ -99,13 +99,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="0">
-        <v>749.57490946220378</v>
+        <v>721.18189187126336</v>
       </c>
       <c r="C2" s="0">
-        <v>192.16671859878784</v>
+        <v>317.24983717232072</v>
       </c>
       <c r="D2" s="0">
-        <v>144043.35069533519</v>
+        <v>228794.83776778451</v>
       </c>
     </row>
     <row r="3">
@@ -113,13 +113,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="0">
-        <v>754.35943958072608</v>
+        <v>724.18323456929693</v>
       </c>
       <c r="C3" s="0">
-        <v>271.89271479488105</v>
+        <v>396.5576523318972</v>
       </c>
       <c r="D3" s="0">
-        <v>205104.83595874865</v>
+        <v>287180.40335892001</v>
       </c>
     </row>
     <row r="4">
@@ -127,13 +127,13 @@
         <v>10</v>
       </c>
       <c r="B4" s="0">
-        <v>763.76557912969372</v>
+        <v>733.13865958881252</v>
       </c>
       <c r="C4" s="0">
-        <v>337.07648015038296</v>
+        <v>461.63145515915699</v>
       </c>
       <c r="D4" s="0">
-        <v>257447.41307305594</v>
+        <v>338439.86625941738</v>
       </c>
     </row>
     <row r="5">
@@ -141,13 +141,13 @@
         <v>15</v>
       </c>
       <c r="B5" s="0">
-        <v>776.79992559284892</v>
+        <v>746.13831744707431</v>
       </c>
       <c r="C5" s="0">
-        <v>396.70096919848209</v>
+        <v>521.2474094764558</v>
       </c>
       <c r="D5" s="0">
-        <v>308157.28335599194</v>
+        <v>388922.66508040891</v>
       </c>
     </row>
     <row r="6">
@@ -155,13 +155,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="0">
-        <v>793.12280296662641</v>
+        <v>762.62657541713418</v>
       </c>
       <c r="C6" s="0">
-        <v>452.52553716383</v>
+        <v>577.11257543527108</v>
       </c>
       <c r="D6" s="0">
-        <v>358908.3224493551</v>
+        <v>440121.38703436329</v>
       </c>
     </row>
     <row r="7">
@@ -169,13 +169,13 @@
         <v>25</v>
       </c>
       <c r="B7" s="0">
-        <v>812.51719945469085</v>
+        <v>782.30542345251774</v>
       </c>
       <c r="C7" s="0">
-        <v>504.93607747696467</v>
+        <v>629.59239938160954</v>
       </c>
       <c r="D7" s="0">
-        <v>410269.24757522013</v>
+        <v>492533.54860071675</v>
       </c>
     </row>
     <row r="8">
@@ -183,13 +183,13 @@
         <v>30</v>
       </c>
       <c r="B8" s="0">
-        <v>834.79379463241367</v>
+        <v>804.94920858940031</v>
       </c>
       <c r="C8" s="0">
-        <v>553.88007288036897</v>
+        <v>678.62481498969032</v>
       </c>
       <c r="D8" s="0">
-        <v>462375.64781108103</v>
+        <v>546258.50775507942</v>
       </c>
     </row>
     <row r="9">
@@ -197,13 +197,13 @@
         <v>35</v>
       </c>
       <c r="B9" s="0">
-        <v>859.76312529369409</v>
+        <v>830.351083056721</v>
       </c>
       <c r="C9" s="0">
-        <v>599.13373360342598</v>
+        <v>723.98116758366609</v>
       </c>
       <c r="D9" s="0">
-        <v>515113.09127176105</v>
+        <v>601158.5466157666</v>
       </c>
     </row>
     <row r="10">
@@ -211,13 +211,13 @@
         <v>40</v>
       </c>
       <c r="B10" s="0">
-        <v>887.22578825402184</v>
+        <v>858.30376212375108</v>
       </c>
       <c r="C10" s="0">
-        <v>640.40136484783443</v>
+        <v>765.36322464721445</v>
       </c>
       <c r="D10" s="0">
-        <v>568180.60572607129</v>
+        <v>656914.13510586985</v>
       </c>
     </row>
     <row r="11">
@@ -225,13 +225,13 @@
         <v>45</v>
       </c>
       <c r="B11" s="0">
-        <v>916.96893076443519</v>
+        <v>888.59202279444366</v>
       </c>
       <c r="C11" s="0">
-        <v>677.35870942295401</v>
+        <v>802.44548368011761</v>
       </c>
       <c r="D11" s="0">
-        <v>621116.89152354386</v>
+        <v>713046.65552558145</v>
       </c>
     </row>
     <row r="12">
@@ -239,13 +239,13 @@
         <v>50</v>
       </c>
       <c r="B12" s="0">
-        <v>948.76532462207956</v>
+        <v>920.9899838428878</v>
       </c>
       <c r="C12" s="0">
-        <v>709.67373718544059</v>
+        <v>834.89546231570591</v>
       </c>
       <c r="D12" s="0">
-        <v>673313.83363650891</v>
+        <v>768930.35834864236</v>
       </c>
     </row>
     <row r="13">
@@ -253,13 +253,13 @@
         <v>55</v>
       </c>
       <c r="B13" s="0">
-        <v>982.37362214554162</v>
+        <v>955.26059982514153</v>
       </c>
       <c r="C13" s="0">
-        <v>737.01679849846698</v>
+        <v>862.38359641822478</v>
       </c>
       <c r="D13" s="0">
-        <v>724025.86192304979</v>
+        <v>823801.07159383618</v>
       </c>
     </row>
     <row r="14">
@@ -267,13 +267,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="0">
-        <v>1017.5391703716315</v>
+        <v>991.15628784853254</v>
       </c>
       <c r="C14" s="0">
-        <v>759.0647943571654</v>
+        <v>884.58727644612145</v>
       </c>
       <c r="D14" s="0">
-        <v>772378.16110850312</v>
+        <v>876764.24120038143</v>
       </c>
     </row>
     <row r="15">
@@ -281,13 +281,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="0">
-        <v>1053.9950424142089</v>
+        <v>1028.4201730270577</v>
       </c>
       <c r="C15" s="0">
-        <v>775.50111635450014</v>
+        <v>901.19071837403908</v>
       </c>
       <c r="D15" s="0">
-        <v>817374.33202432771</v>
+        <v>926802.71452060773</v>
       </c>
     </row>
     <row r="16">
@@ -295,13 +295,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="0">
-        <v>1091.4630303772233</v>
+        <v>1066.7876658444998</v>
       </c>
       <c r="C16" s="0">
-        <v>786.01167976574823</v>
+        <v>911.88096269521088</v>
       </c>
       <c r="D16" s="0">
-        <v>857902.6899090152</v>
+        <v>972783.36372165941</v>
       </c>
     </row>
     <row r="17">
@@ -309,13 +309,13 @@
         <v>75</v>
       </c>
       <c r="B17" s="0">
-        <v>1129.6543193869115</v>
+        <v>1105.9881601704744</v>
       </c>
       <c r="C17" s="0">
-        <v>793.79861087035783</v>
+        <v>916.33930775375109</v>
       </c>
       <c r="D17" s="0">
-        <v>896718.02949302993</v>
+        <v>1013460.4250744573</v>
       </c>
     </row>
     <row r="18">
@@ -323,13 +323,13 @@
         <v>80</v>
       </c>
       <c r="B18" s="0">
-        <v>1168.2694286799262</v>
+        <v>1145.7466176480414</v>
       </c>
       <c r="C18" s="0">
-        <v>796.83450709137242</v>
+        <v>914.22639594845941</v>
       </c>
       <c r="D18" s="0">
-        <v>930917.39435208833</v>
+        <v>1047471.8009225064</v>
       </c>
     </row>
     <row r="19">
@@ -337,13 +337,13 @@
         <v>85</v>
       </c>
       <c r="B19" s="0">
-        <v>1206.9966952336056</v>
+        <v>1185.7846637662365</v>
       </c>
       <c r="C19" s="0">
-        <v>793.67001186378479</v>
+        <v>905.15749474800464</v>
       </c>
       <c r="D19" s="0">
-        <v>957957.08142560476</v>
+        <v>1073321.8755652516</v>
       </c>
     </row>
     <row r="20">
@@ -351,13 +351,13 @@
         <v>90</v>
       </c>
       <c r="B20" s="0">
-        <v>1245.5078988954349</v>
+        <v>1225.8204562473786</v>
       </c>
       <c r="C20" s="0">
-        <v>784.04360861304622</v>
+        <v>888.66143150626897</v>
       </c>
       <c r="D20" s="0">
-        <v>976532.50760602986</v>
+        <v>1089339.3614184633</v>
       </c>
     </row>
     <row r="21">
@@ -365,13 +365,13 @@
         <v>95</v>
       </c>
       <c r="B21" s="0">
-        <v>1307.1893226825234</v>
+        <v>1289.3069153111589</v>
       </c>
       <c r="C21" s="0">
-        <v>767.62883396882</v>
+        <v>864.11035824295891</v>
       </c>
       <c r="D21" s="0">
-        <v>1003436.215547277</v>
+        <v>1114103.4604746499</v>
       </c>
     </row>
     <row r="22">
@@ -379,13 +379,13 @@
         <v>100</v>
       </c>
       <c r="B22" s="0">
-        <v>1367.7147950669782</v>
+        <v>1352.0175686629702</v>
       </c>
       <c r="C22" s="0">
-        <v>743.96612021033957</v>
+        <v>830.59353314043449</v>
       </c>
       <c r="D22" s="0">
-        <v>1017533.4696402595</v>
+        <v>1122977.0492237164</v>
       </c>
     </row>
     <row r="23">
@@ -393,13 +393,13 @@
         <v>105</v>
       </c>
       <c r="B23" s="0">
-        <v>1426.3997848583081</v>
+        <v>1413.4252579020172</v>
       </c>
       <c r="C23" s="0">
-        <v>712.33102031441308</v>
+        <v>786.67385182756288</v>
       </c>
       <c r="D23" s="0">
-        <v>1016068.8141243779</v>
+        <v>1111904.6919041462</v>
       </c>
     </row>
     <row r="24">
@@ -407,13 +407,13 @@
         <v>110</v>
       </c>
       <c r="B24" s="0">
-        <v>1482.3338326520243</v>
+        <v>1472.8869020475863</v>
       </c>
       <c r="C24" s="0">
-        <v>671.45323989271492</v>
+        <v>729.86918355829118</v>
       </c>
       <c r="D24" s="0">
-        <v>995317.85453678714</v>
+        <v>1075014.7606711725</v>
       </c>
     </row>
     <row r="25">
@@ -421,13 +421,13 @@
         <v>115</v>
       </c>
       <c r="B25" s="0">
-        <v>1534.0190566554104</v>
+        <v>1529.4108256751295</v>
       </c>
       <c r="C25" s="0">
-        <v>618.82450138813113</v>
+        <v>655.3745328594913</v>
       </c>
       <c r="D25" s="0">
-        <v>949288.57785467559</v>
+        <v>1002336.9054270869</v>
       </c>
     </row>
     <row r="26">
@@ -435,13 +435,13 @@
         <v>120</v>
       </c>
       <c r="B26" s="0">
-        <v>1578.0613435288069</v>
+        <v>1580.75050658341</v>
       </c>
       <c r="C26" s="0">
-        <v>548.54007705640459</v>
+        <v>552.07109398706075</v>
       </c>
       <c r="D26" s="0">
-        <v>865629.89097902505</v>
+        <v>872686.6614901037</v>
       </c>
     </row>
   </sheetData>
@@ -478,13 +478,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="0">
-        <v>749.57490946220378</v>
+        <v>761.23831235875093</v>
       </c>
       <c r="C2" s="0">
-        <v>192.16671859878619</v>
+        <v>227.85929594485208</v>
       </c>
       <c r="D2" s="0">
-        <v>144043.35069533394</v>
+        <v>173455.22590031236</v>
       </c>
     </row>
     <row r="3">
@@ -492,13 +492,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="0">
-        <v>754.35943958072608</v>
+        <v>763.55377057003204</v>
       </c>
       <c r="C3" s="0">
-        <v>271.8927147948815</v>
+        <v>321.59868152706906</v>
       </c>
       <c r="D3" s="0">
-        <v>205104.835958749</v>
+        <v>245557.88589034448</v>
       </c>
     </row>
     <row r="4">
@@ -506,13 +506,13 @@
         <v>10</v>
       </c>
       <c r="B4" s="0">
-        <v>763.76557912969372</v>
+        <v>772.44581823758108</v>
       </c>
       <c r="C4" s="0">
-        <v>337.0764801503833</v>
+        <v>389.13234938420442</v>
       </c>
       <c r="D4" s="0">
-        <v>257447.4130730562</v>
+        <v>300583.65602279408</v>
       </c>
     </row>
     <row r="5">
@@ -520,13 +520,13 @@
         <v>15</v>
       </c>
       <c r="B5" s="0">
-        <v>776.79992559284892</v>
+        <v>785.33569826039775</v>
       </c>
       <c r="C5" s="0">
-        <v>396.70096919848226</v>
+        <v>449.67442900751735</v>
       </c>
       <c r="D5" s="0">
-        <v>308157.28335599206</v>
+        <v>353145.38169446431</v>
       </c>
     </row>
     <row r="6">
@@ -534,13 +534,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="0">
-        <v>793.12280296662641</v>
+        <v>801.66231265908982</v>
       </c>
       <c r="C6" s="0">
-        <v>452.52553716383005</v>
+        <v>505.96762793760377</v>
       </c>
       <c r="D6" s="0">
-        <v>358908.32244935515</v>
+        <v>405615.17874309333</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>25</v>
       </c>
       <c r="B7" s="0">
-        <v>812.51719945469085</v>
+        <v>821.13786384934338</v>
       </c>
       <c r="C7" s="0">
-        <v>504.93607747696512</v>
+        <v>558.66018993291607</v>
       </c>
       <c r="D7" s="0">
-        <v>410269.24757522048</v>
+        <v>458737.03497918317</v>
       </c>
     </row>
     <row r="8">
@@ -562,13 +562,13 @@
         <v>30</v>
       </c>
       <c r="B8" s="0">
-        <v>834.79379463241367</v>
+        <v>843.54367849010441</v>
       </c>
       <c r="C8" s="0">
-        <v>553.88007288036909</v>
+        <v>607.79742115900399</v>
       </c>
       <c r="D8" s="0">
-        <v>462375.64781108115</v>
+        <v>512703.67242126545</v>
       </c>
     </row>
     <row r="9">
@@ -576,13 +576,13 @@
         <v>35</v>
       </c>
       <c r="B9" s="0">
-        <v>859.76312529369409</v>
+        <v>868.67655374977267</v>
       </c>
       <c r="C9" s="0">
-        <v>599.13373360342587</v>
+        <v>653.19979673870864</v>
       </c>
       <c r="D9" s="0">
-        <v>515113.09127176099</v>
+        <v>567419.34834103345</v>
       </c>
     </row>
     <row r="10">
@@ -590,13 +590,13 @@
         <v>40</v>
       </c>
       <c r="B10" s="0">
-        <v>887.22578825402184</v>
+        <v>896.33045373357709</v>
       </c>
       <c r="C10" s="0">
-        <v>640.40136484783454</v>
+        <v>694.59474963182731</v>
       </c>
       <c r="D10" s="0">
-        <v>568180.6057260714</v>
+        <v>622586.42709845619</v>
       </c>
     </row>
     <row r="11">
@@ -604,13 +604,13 @@
         <v>45</v>
       </c>
       <c r="B11" s="0">
-        <v>916.96893076443519</v>
+        <v>926.28964065351954</v>
       </c>
       <c r="C11" s="0">
-        <v>677.35870942295389</v>
+        <v>731.67181597156514</v>
       </c>
       <c r="D11" s="0">
-        <v>621116.89152354375</v>
+        <v>677740.02349260915</v>
       </c>
     </row>
     <row r="12">
@@ -618,13 +618,13 @@
         <v>50</v>
       </c>
       <c r="B12" s="0">
-        <v>948.76532462207956</v>
+        <v>958.32628175210903</v>
       </c>
       <c r="C12" s="0">
-        <v>709.67373718544059</v>
+        <v>764.10845325444063</v>
       </c>
       <c r="D12" s="0">
-        <v>673313.83363650891</v>
+        <v>732265.21286268334</v>
       </c>
     </row>
     <row r="13">
@@ -632,13 +632,13 @@
         <v>55</v>
       </c>
       <c r="B13" s="0">
-        <v>982.37362214554162</v>
+        <v>992.20005358601952</v>
       </c>
       <c r="C13" s="0">
-        <v>737.01679849846698</v>
+        <v>791.58266390518656</v>
       </c>
       <c r="D13" s="0">
-        <v>724025.86192304979</v>
+        <v>785408.36154449021</v>
       </c>
     </row>
     <row r="14">
@@ -646,13 +646,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="0">
-        <v>1017.5391703716315</v>
+        <v>1027.6587164183325</v>
       </c>
       <c r="C14" s="0">
-        <v>759.06479435716562</v>
+        <v>813.77860352897449</v>
       </c>
       <c r="D14" s="0">
-        <v>772378.16110850335</v>
+        <v>836286.67515128898</v>
       </c>
     </row>
     <row r="15">
@@ -660,13 +660,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="0">
-        <v>1053.9950424142089</v>
+        <v>1064.4391626312222</v>
       </c>
       <c r="C15" s="0">
-        <v>775.50111635450025</v>
+        <v>830.38757818785336</v>
       </c>
       <c r="D15" s="0">
-        <v>817374.33202432783</v>
+        <v>883897.05838564713</v>
       </c>
     </row>
     <row r="16">
@@ -674,13 +674,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="0">
-        <v>1091.4630303772233</v>
+        <v>1102.2686409145833</v>
       </c>
       <c r="C16" s="0">
-        <v>786.01167976574811</v>
+        <v>841.10510406984304</v>
       </c>
       <c r="D16" s="0">
-        <v>857902.68990901508</v>
+        <v>927123.77992938506</v>
       </c>
     </row>
     <row r="17">
@@ -688,13 +688,13 @@
         <v>75</v>
       </c>
       <c r="B17" s="0">
-        <v>1129.6543193869115</v>
+        <v>1140.8659045817494</v>
       </c>
       <c r="C17" s="0">
-        <v>793.79861087035783</v>
+        <v>845.62363006229771</v>
       </c>
       <c r="D17" s="0">
-        <v>896718.02949302993</v>
+        <v>964743.16764672589</v>
       </c>
     </row>
     <row r="18">
@@ -702,13 +702,13 @@
         <v>80</v>
       </c>
       <c r="B18" s="0">
-        <v>1168.2694286799262</v>
+        <v>1179.941973414323</v>
       </c>
       <c r="C18" s="0">
-        <v>796.83450709137242</v>
+        <v>843.61949431043649</v>
       </c>
       <c r="D18" s="0">
-        <v>930917.39435208833</v>
+        <v>995422.05092744972</v>
       </c>
     </row>
     <row r="19">
@@ -716,13 +716,13 @@
         <v>85</v>
       </c>
       <c r="B19" s="0">
-        <v>1206.9966952336056</v>
+        <v>1219.2000060937144</v>
       </c>
       <c r="C19" s="0">
-        <v>793.67001186378479</v>
+        <v>834.73123010602205</v>
       </c>
       <c r="D19" s="0">
-        <v>957957.08142560476</v>
+        <v>1017704.3208318758</v>
       </c>
     </row>
     <row r="20">
@@ -730,13 +730,13 @@
         <v>90</v>
       </c>
       <c r="B20" s="0">
-        <v>1245.5078988954351</v>
+        <v>1258.3333360390548</v>
       </c>
       <c r="C20" s="0">
-        <v>784.04360861304622</v>
+        <v>818.52377466435041</v>
       </c>
       <c r="D20" s="0">
-        <v>976532.50760603009</v>
+        <v>1029975.7520006716</v>
       </c>
     </row>
     <row r="21">
@@ -744,13 +744,13 @@
         <v>95</v>
       </c>
       <c r="B21" s="0">
-        <v>1307.1893226825234</v>
+        <v>1320.7609342425303</v>
       </c>
       <c r="C21" s="0">
-        <v>767.62883396882</v>
+        <v>794.42806420496663</v>
       </c>
       <c r="D21" s="0">
-        <v>1003436.215547277</v>
+        <v>1049249.5522678366</v>
       </c>
     </row>
     <row r="22">
@@ -758,13 +758,13 @@
         <v>100</v>
       </c>
       <c r="B22" s="0">
-        <v>1367.7147950669782</v>
+        <v>1382.2090872802974</v>
       </c>
       <c r="C22" s="0">
-        <v>743.96612021033957</v>
+        <v>761.63452648959378</v>
       </c>
       <c r="D22" s="0">
-        <v>1017533.4696402595</v>
+        <v>1052738.1637003429</v>
       </c>
     </row>
     <row r="23">
@@ -772,13 +772,13 @@
         <v>105</v>
       </c>
       <c r="B23" s="0">
-        <v>1426.3997848583081</v>
+        <v>1442.0841267439018</v>
       </c>
       <c r="C23" s="0">
-        <v>712.33102031441308</v>
+        <v>718.89286450308293</v>
       </c>
       <c r="D23" s="0">
-        <v>1016068.8141243779</v>
+        <v>1036703.9887293505</v>
       </c>
     </row>
     <row r="24">
@@ -786,13 +786,13 @@
         <v>110</v>
       </c>
       <c r="B24" s="0">
-        <v>1482.3338326520243</v>
+        <v>1499.6506324499846</v>
       </c>
       <c r="C24" s="0">
-        <v>671.45323989271492</v>
+        <v>664.10046455938846</v>
       </c>
       <c r="D24" s="0">
-        <v>995317.85453678714</v>
+        <v>995918.68168681546</v>
       </c>
     </row>
     <row r="25">
@@ -800,13 +800,13 @@
         <v>115</v>
       </c>
       <c r="B25" s="0">
-        <v>1534.0190566554104</v>
+        <v>1553.8054085868216</v>
       </c>
       <c r="C25" s="0">
-        <v>618.82450138813113</v>
+        <v>611.42682983656334</v>
       </c>
       <c r="D25" s="0">
-        <v>949288.57785467559</v>
+        <v>950038.31515514641</v>
       </c>
     </row>
     <row r="26">
@@ -814,13 +814,13 @@
         <v>120</v>
       </c>
       <c r="B26" s="0">
-        <v>1578.0613435288069</v>
+        <v>1602.3103506098066</v>
       </c>
       <c r="C26" s="0">
-        <v>548.54007705640459</v>
+        <v>546.13608401825934</v>
       </c>
       <c r="D26" s="0">
-        <v>865629.89097902505</v>
+        <v>875079.50026396394</v>
       </c>
     </row>
   </sheetData>

--- a/Interim3/ENME473_Q7_BoxDimensions.xlsx
+++ b/Interim3/ENME473_Q7_BoxDimensions.xlsx
@@ -478,13 +478,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="0">
-        <v>761.23831235875093</v>
+        <v>832.46895056959727</v>
       </c>
       <c r="C2" s="0">
-        <v>227.85929594485208</v>
+        <v>137.11917205240047</v>
       </c>
       <c r="D2" s="0">
-        <v>173455.22590031236</v>
+        <v>114147.45326143387</v>
       </c>
     </row>
     <row r="3">
@@ -492,13 +492,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="0">
-        <v>763.55377057003204</v>
+        <v>836.24929120518345</v>
       </c>
       <c r="C3" s="0">
-        <v>321.59868152706906</v>
+        <v>240.78935819092459</v>
       </c>
       <c r="D3" s="0">
-        <v>245557.88589034448</v>
+        <v>201359.93011691171</v>
       </c>
     </row>
     <row r="4">
@@ -506,13 +506,13 @@
         <v>10</v>
       </c>
       <c r="B4" s="0">
-        <v>772.44581823758108</v>
+        <v>845.49858312141623</v>
       </c>
       <c r="C4" s="0">
-        <v>389.13234938420442</v>
+        <v>309.75261914314609</v>
       </c>
       <c r="D4" s="0">
-        <v>300583.65602279408</v>
+        <v>261895.4006036777</v>
       </c>
     </row>
     <row r="5">
@@ -520,13 +520,13 @@
         <v>15</v>
       </c>
       <c r="B5" s="0">
-        <v>785.33569826039775</v>
+        <v>858.4401461782328</v>
       </c>
       <c r="C5" s="0">
-        <v>449.67442900751735</v>
+        <v>370.74467979663336</v>
       </c>
       <c r="D5" s="0">
-        <v>353145.38169446431</v>
+        <v>318262.11711942405</v>
       </c>
     </row>
     <row r="6">
@@ -534,13 +534,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="0">
-        <v>801.66231265908982</v>
+        <v>874.67903719724472</v>
       </c>
       <c r="C6" s="0">
-        <v>505.96762793760377</v>
+        <v>427.15835056453733</v>
       </c>
       <c r="D6" s="0">
-        <v>405615.17874309333</v>
+        <v>373626.45480255265</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>25</v>
       </c>
       <c r="B7" s="0">
-        <v>821.13786384934338</v>
+        <v>893.98616237047918</v>
       </c>
       <c r="C7" s="0">
-        <v>558.66018993291607</v>
+        <v>479.8175876563248</v>
       </c>
       <c r="D7" s="0">
-        <v>458737.03497918317</v>
+        <v>428950.28382673883</v>
       </c>
     </row>
     <row r="8">
@@ -562,13 +562,13 @@
         <v>30</v>
       </c>
       <c r="B8" s="0">
-        <v>843.54367849010441</v>
+        <v>916.16847861785027</v>
       </c>
       <c r="C8" s="0">
-        <v>607.79742115900399</v>
+        <v>528.8351082637148</v>
       </c>
       <c r="D8" s="0">
-        <v>512703.67242126545</v>
+        <v>484502.05657767371</v>
       </c>
     </row>
     <row r="9">
@@ -576,13 +576,13 @@
         <v>35</v>
       </c>
       <c r="B9" s="0">
-        <v>868.67655374977267</v>
+        <v>941.03491745786221</v>
       </c>
       <c r="C9" s="0">
-        <v>653.19979673870864</v>
+        <v>574.06214941368796</v>
       </c>
       <c r="D9" s="0">
-        <v>567419.34834103345</v>
+        <v>540212.52738919284</v>
       </c>
     </row>
     <row r="10">
@@ -590,13 +590,13 @@
         <v>40</v>
       </c>
       <c r="B10" s="0">
-        <v>896.33045373357709</v>
+        <v>968.38498361179211</v>
       </c>
       <c r="C10" s="0">
-        <v>694.59474963182731</v>
+        <v>615.24156528877461</v>
       </c>
       <c r="D10" s="0">
-        <v>622586.42709845619</v>
+        <v>595790.69311946328</v>
       </c>
     </row>
     <row r="11">
@@ -604,13 +604,13 @@
         <v>45</v>
       </c>
       <c r="B11" s="0">
-        <v>926.28964065351954</v>
+        <v>998.00473693582944</v>
       </c>
       <c r="C11" s="0">
-        <v>731.67181597156514</v>
+        <v>652.07090510774265</v>
       </c>
       <c r="D11" s="0">
-        <v>677740.02349260915</v>
+        <v>650769.85211556091</v>
       </c>
     </row>
     <row r="12">
@@ -618,13 +618,13 @@
         <v>50</v>
       </c>
       <c r="B12" s="0">
-        <v>958.32628175210903</v>
+        <v>1029.665668583041</v>
       </c>
       <c r="C12" s="0">
-        <v>764.10845325444063</v>
+        <v>684.23163816716215</v>
       </c>
       <c r="D12" s="0">
-        <v>732265.21286268334</v>
+        <v>704529.82717906043</v>
       </c>
     </row>
     <row r="13">
@@ -632,13 +632,13 @@
         <v>55</v>
       </c>
       <c r="B13" s="0">
-        <v>992.20005358601952</v>
+        <v>1063.1248515370469</v>
       </c>
       <c r="C13" s="0">
-        <v>791.58266390518656</v>
+        <v>711.40338890365251</v>
       </c>
       <c r="D13" s="0">
-        <v>785408.36154449021</v>
+        <v>756310.62221114757</v>
       </c>
     </row>
     <row r="14">
@@ -646,13 +646,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="0">
-        <v>1027.6587164183325</v>
+        <v>1098.1256709271816</v>
       </c>
       <c r="C14" s="0">
-        <v>813.77860352897449</v>
+        <v>733.27035737934352</v>
       </c>
       <c r="D14" s="0">
-        <v>836286.67515128898</v>
+        <v>805223.00316820585</v>
       </c>
     </row>
     <row r="15">
@@ -660,13 +660,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="0">
-        <v>1064.4391626312222</v>
+        <v>1134.3987664542697</v>
       </c>
       <c r="C15" s="0">
-        <v>830.38757818785336</v>
+        <v>750.82377471453344</v>
       </c>
       <c r="D15" s="0">
-        <v>883897.05838564713</v>
+        <v>851733.56386070524</v>
       </c>
     </row>
     <row r="16">
@@ -674,13 +674,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="0">
-        <v>1102.2686409145833</v>
+        <v>1171.6629202825986</v>
       </c>
       <c r="C16" s="0">
-        <v>841.10510406984304</v>
+        <v>765.73376426729487</v>
       </c>
       <c r="D16" s="0">
-        <v>927123.77992938506</v>
+        <v>897181.85840040573</v>
       </c>
     </row>
     <row r="17">
@@ -688,13 +688,13 @@
         <v>75</v>
       </c>
       <c r="B17" s="0">
-        <v>1140.8659045817494</v>
+        <v>1209.625607514449</v>
       </c>
       <c r="C17" s="0">
-        <v>845.62363006229771</v>
+        <v>774.94579514457632</v>
       </c>
       <c r="D17" s="0">
-        <v>964743.16764672589</v>
+        <v>937394.27824252588</v>
       </c>
     </row>
     <row r="18">
@@ -702,13 +702,13 @@
         <v>80</v>
       </c>
       <c r="B18" s="0">
-        <v>1179.941973414323</v>
+        <v>1247.9828049298872</v>
       </c>
       <c r="C18" s="0">
-        <v>843.61949431043649</v>
+        <v>778.24507525756667</v>
       </c>
       <c r="D18" s="0">
-        <v>995422.05092744972</v>
+        <v>971236.47194280918</v>
       </c>
     </row>
     <row r="19">
@@ -716,13 +716,13 @@
         <v>85</v>
       </c>
       <c r="B19" s="0">
-        <v>1219.2000060937144</v>
+        <v>1286.4173727909151</v>
       </c>
       <c r="C19" s="0">
-        <v>834.73123010602205</v>
+        <v>775.41778683455345</v>
       </c>
       <c r="D19" s="0">
-        <v>1017704.3208318758</v>
+        <v>997510.91215505206</v>
       </c>
     </row>
     <row r="20">
@@ -730,13 +730,13 @@
         <v>90</v>
       </c>
       <c r="B20" s="0">
-        <v>1258.3333360390548</v>
+        <v>1324.5947280552086</v>
       </c>
       <c r="C20" s="0">
-        <v>818.52377466435041</v>
+        <v>766.23335667400693</v>
       </c>
       <c r="D20" s="0">
-        <v>1029975.7520006716</v>
+        <v>1014948.6647104359</v>
       </c>
     </row>
     <row r="21">
@@ -744,13 +744,13 @@
         <v>95</v>
       </c>
       <c r="B21" s="0">
-        <v>1320.7609342425303</v>
+        <v>1385.8944483759385</v>
       </c>
       <c r="C21" s="0">
-        <v>794.42806420496663</v>
+        <v>750.41426091137441</v>
       </c>
       <c r="D21" s="0">
-        <v>1049249.5522678366</v>
+        <v>1039994.9581792068</v>
       </c>
     </row>
     <row r="22">
@@ -758,13 +758,13 @@
         <v>100</v>
       </c>
       <c r="B22" s="0">
-        <v>1382.2090872802974</v>
+        <v>1445.9853774056996</v>
       </c>
       <c r="C22" s="0">
-        <v>761.63452648959378</v>
+        <v>727.58272619971535</v>
       </c>
       <c r="D22" s="0">
-        <v>1052738.1637003429</v>
+        <v>1052073.9829377632</v>
       </c>
     </row>
     <row r="23">
@@ -772,13 +772,13 @@
         <v>105</v>
       </c>
       <c r="B23" s="0">
-        <v>1442.0841267439018</v>
+        <v>1504.1865450010093</v>
       </c>
       <c r="C23" s="0">
-        <v>718.89286450308293</v>
+        <v>697.16094635783361</v>
       </c>
       <c r="D23" s="0">
-        <v>1036703.9887293505</v>
+        <v>1048660.1152116237</v>
       </c>
     </row>
     <row r="24">
@@ -786,13 +786,13 @@
         <v>110</v>
       </c>
       <c r="B24" s="0">
-        <v>1499.6506324499846</v>
+        <v>1559.6227044165041</v>
       </c>
       <c r="C24" s="0">
-        <v>664.10046455938846</v>
+        <v>658.16769180109384</v>
       </c>
       <c r="D24" s="0">
-        <v>995918.68168681546</v>
+        <v>1026493.2754463902</v>
       </c>
     </row>
     <row r="25">
@@ -800,13 +800,13 @@
         <v>115</v>
       </c>
       <c r="B25" s="0">
-        <v>1553.8054085868216</v>
+        <v>1610.9512582816076</v>
       </c>
       <c r="C25" s="0">
-        <v>611.42682983656334</v>
+        <v>608.74958206735619</v>
       </c>
       <c r="D25" s="0">
-        <v>950038.31515514641</v>
+        <v>980665.90520981024</v>
       </c>
     </row>
     <row r="26">
@@ -814,13 +814,13 @@
         <v>120</v>
       </c>
       <c r="B26" s="0">
-        <v>1602.3103506098066</v>
+        <v>1655.4905653908636</v>
       </c>
       <c r="C26" s="0">
-        <v>546.13608401825934</v>
+        <v>544.87455903441446</v>
       </c>
       <c r="D26" s="0">
-        <v>875079.50026396394</v>
+        <v>902034.69180298026</v>
       </c>
     </row>
   </sheetData>

--- a/Interim3/ENME473_Q7_BoxDimensions.xlsx
+++ b/Interim3/ENME473_Q7_BoxDimensions.xlsx
@@ -71,7 +71,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.42578125" customWidth="true"/>
@@ -110,337 +110,1681 @@
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B3" s="0">
-        <v>724.18323456929693</v>
+        <v>721.03238221838638</v>
       </c>
       <c r="C3" s="0">
-        <v>396.5576523318972</v>
+        <v>335.64999477767901</v>
       </c>
       <c r="D3" s="0">
-        <v>287180.40335892001</v>
+        <v>242014.51532613885</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B4" s="0">
-        <v>733.13865958881252</v>
+        <v>721.35358114824749</v>
       </c>
       <c r="C4" s="0">
-        <v>461.63145515915699</v>
+        <v>352.27075367094955</v>
       </c>
       <c r="D4" s="0">
-        <v>338439.86625941738</v>
+        <v>254111.7696943316</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B5" s="0">
-        <v>746.13831744707431</v>
+        <v>722.02539419921925</v>
       </c>
       <c r="C5" s="0">
-        <v>521.2474094764558</v>
+        <v>367.7576700032451</v>
       </c>
       <c r="D5" s="0">
-        <v>388922.66508040891</v>
+        <v>265530.37665387942</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B6" s="0">
-        <v>762.62657541713418</v>
+        <v>722.98210040007041</v>
       </c>
       <c r="C6" s="0">
-        <v>577.11257543527108</v>
+        <v>382.45220827946105</v>
       </c>
       <c r="D6" s="0">
-        <v>440121.38703436329</v>
+        <v>276506.10084452992</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B7" s="0">
-        <v>782.30542345251774</v>
+        <v>724.18323456929693</v>
       </c>
       <c r="C7" s="0">
-        <v>629.59239938160954</v>
+        <v>396.5576523318972</v>
       </c>
       <c r="D7" s="0">
-        <v>492533.54860071675</v>
+        <v>287180.40335892001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="B8" s="0">
-        <v>804.94920858940031</v>
+        <v>725.60187373545193</v>
       </c>
       <c r="C8" s="0">
-        <v>678.62481498969032</v>
+        <v>410.20457048559194</v>
       </c>
       <c r="D8" s="0">
-        <v>546258.50775507942</v>
+        <v>297645.20495919179</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="B9" s="0">
-        <v>830.351083056721</v>
+        <v>727.21907778942989</v>
       </c>
       <c r="C9" s="0">
-        <v>723.98116758366609</v>
+        <v>423.48134373837132</v>
       </c>
       <c r="D9" s="0">
-        <v>601158.5466157666</v>
+        <v>307963.71225444693</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="B10" s="0">
-        <v>858.30376212375108</v>
+        <v>729.02094000271609</v>
       </c>
       <c r="C10" s="0">
-        <v>765.36322464721445</v>
+        <v>436.45010290609389</v>
       </c>
       <c r="D10" s="0">
-        <v>656914.13510586985</v>
+        <v>318181.26428488275</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="B11" s="0">
-        <v>888.59202279444366</v>
+        <v>730.99689064361439</v>
       </c>
       <c r="C11" s="0">
-        <v>802.44548368011761</v>
+        <v>449.15575977958611</v>
       </c>
       <c r="D11" s="0">
-        <v>713046.65552558145</v>
+        <v>328331.46381354763</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="B12" s="0">
-        <v>920.9899838428878</v>
+        <v>733.13865958881252</v>
       </c>
       <c r="C12" s="0">
-        <v>834.89546231570591</v>
+        <v>461.63145515915699</v>
       </c>
       <c r="D12" s="0">
-        <v>768930.35834864236</v>
+        <v>338439.86625941738</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="B13" s="0">
-        <v>955.26059982514153</v>
+        <v>735.43961057961178</v>
       </c>
       <c r="C13" s="0">
-        <v>862.38359641822478</v>
+        <v>473.9020117084051</v>
       </c>
       <c r="D13" s="0">
-        <v>823801.07159383618</v>
+        <v>348526.31094372406</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="B14" s="0">
-        <v>991.15628784853254</v>
+        <v>737.89429701918016</v>
       </c>
       <c r="C14" s="0">
-        <v>884.58727644612145</v>
+        <v>485.98621163954169</v>
       </c>
       <c r="D14" s="0">
-        <v>876764.24120038143</v>
+        <v>358606.45399877412</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="B15" s="0">
-        <v>1028.4201730270577</v>
+        <v>740.49815592654136</v>
       </c>
       <c r="C15" s="0">
-        <v>901.19071837403908</v>
+        <v>497.89834977900233</v>
       </c>
       <c r="D15" s="0">
-        <v>926802.71452060773</v>
+        <v>368692.80985021929</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="B16" s="0">
-        <v>1066.7876658444998</v>
+        <v>743.2472913338645</v>
       </c>
       <c r="C16" s="0">
-        <v>911.88096269521088</v>
+        <v>509.6493224774066</v>
       </c>
       <c r="D16" s="0">
-        <v>972783.36372165941</v>
+        <v>378795.47846147168</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="B17" s="0">
-        <v>1105.9881601704744</v>
+        <v>746.13831744707431</v>
       </c>
       <c r="C17" s="0">
-        <v>916.33930775375109</v>
+        <v>521.2474094764558</v>
       </c>
       <c r="D17" s="0">
-        <v>1013460.4250744573</v>
+        <v>388922.66508040891</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="B18" s="0">
-        <v>1145.7466176480414</v>
+        <v>749.1682428308693</v>
       </c>
       <c r="C18" s="0">
-        <v>914.22639594845941</v>
+        <v>532.69884698466421</v>
       </c>
       <c r="D18" s="0">
-        <v>1047471.8009225064</v>
+        <v>399081.05915353104</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="B19" s="0">
-        <v>1185.7846637662365</v>
+        <v>752.33438341985106</v>
       </c>
       <c r="C19" s="0">
-        <v>905.15749474800464</v>
+        <v>544.00825534038199</v>
       </c>
       <c r="D19" s="0">
-        <v>1073321.8755652516</v>
+        <v>409276.11535681516</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="B20" s="0">
-        <v>1225.8204562473786</v>
+        <v>755.63429620172087</v>
       </c>
       <c r="C20" s="0">
-        <v>888.66143150626897</v>
+        <v>555.17896326220603</v>
       </c>
       <c r="D20" s="0">
-        <v>1089339.3614184633</v>
+        <v>419512.2651706381</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="B21" s="0">
-        <v>1289.3069153111589</v>
+        <v>759.065727993819</v>
       </c>
       <c r="C21" s="0">
-        <v>864.11035824295891</v>
+        <v>566.21325718597734</v>
       </c>
       <c r="D21" s="0">
-        <v>1114103.4604746499</v>
+        <v>429793.07826562534</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="B22" s="0">
-        <v>1352.0175686629702</v>
+        <v>762.62657541713418</v>
       </c>
       <c r="C22" s="0">
-        <v>830.59353314043449</v>
+        <v>577.11257543527108</v>
       </c>
       <c r="D22" s="0">
-        <v>1122977.0492237164</v>
+        <v>440121.38703436329</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="B23" s="0">
-        <v>1413.4252579020172</v>
+        <v>766.31485329700831</v>
       </c>
       <c r="C23" s="0">
-        <v>786.67385182756288</v>
+        <v>587.87766116532816</v>
       </c>
       <c r="D23" s="0">
-        <v>1111904.6919041462</v>
+        <v>450499.38367249683</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0">
-        <v>110</v>
+        <v>22</v>
       </c>
       <c r="B24" s="0">
-        <v>1472.8869020475863</v>
+        <v>770.12866948750093</v>
       </c>
       <c r="C24" s="0">
-        <v>729.86918355829118</v>
+        <v>598.50868408684198</v>
       </c>
       <c r="D24" s="0">
-        <v>1075014.7606711725</v>
+        <v>460928.69655251462</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>115</v>
+        <v>23</v>
       </c>
       <c r="B25" s="0">
-        <v>1529.4108256751295</v>
+        <v>774.06620464991761</v>
       </c>
       <c r="C25" s="0">
-        <v>655.3745328594913</v>
+        <v>609.00533826142964</v>
       </c>
       <c r="D25" s="0">
-        <v>1002336.9054270869</v>
+        <v>471410.45079956408</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0">
+        <v>24</v>
+      </c>
+      <c r="B26" s="0">
+        <v>778.1256958929855</v>
+      </c>
+      <c r="C26" s="0">
+        <v>619.36692135550652</v>
+      </c>
+      <c r="D26" s="0">
+        <v>481945.31669284956</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0">
+        <v>25</v>
+      </c>
+      <c r="B27" s="0">
+        <v>782.30542345251774</v>
+      </c>
+      <c r="C27" s="0">
+        <v>629.59239938160954</v>
+      </c>
+      <c r="D27" s="0">
+        <v>492533.54860071675</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0">
+        <v>26</v>
+      </c>
+      <c r="B28" s="0">
+        <v>786.60369978498466</v>
+      </c>
+      <c r="C28" s="0">
+        <v>639.68045997522336</v>
+      </c>
+      <c r="D28" s="0">
+        <v>503175.01649667148</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0">
+        <v>27</v>
+      </c>
+      <c r="B29" s="0">
+        <v>791.01886059411538</v>
+      </c>
+      <c r="C29" s="0">
+        <v>649.62955653704296</v>
+      </c>
+      <c r="D29" s="0">
+        <v>513869.23162019218</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0">
+        <v>28</v>
+      </c>
+      <c r="B30" s="0">
+        <v>795.54925741741499</v>
+      </c>
+      <c r="C30" s="0">
+        <v>659.4379450389838</v>
+      </c>
+      <c r="D30" s="0">
+        <v>524615.36748862965</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0">
+        <v>29</v>
+      </c>
+      <c r="B31" s="0">
+        <v>800.19325148057817</v>
+      </c>
+      <c r="C31" s="0">
+        <v>669.10371489410602</v>
+      </c>
+      <c r="D31" s="0">
+        <v>535412.27719884843</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0">
+        <v>30</v>
+      </c>
+      <c r="B32" s="0">
+        <v>804.94920858940031</v>
+      </c>
+      <c r="C32" s="0">
+        <v>678.62481498969032</v>
+      </c>
+      <c r="D32" s="0">
+        <v>546258.50775507942</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0">
+        <v>31</v>
+      </c>
+      <c r="B33" s="0">
+        <v>809.81549487605616</v>
+      </c>
+      <c r="C33" s="0">
+        <v>687.99907575296822</v>
+      </c>
+      <c r="D33" s="0">
+        <v>557152.31200515921</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0">
+        <v>32</v>
+      </c>
+      <c r="B34" s="0">
+        <v>814.79047325314855</v>
+      </c>
+      <c r="C34" s="0">
+        <v>697.22422794216493</v>
+      </c>
+      <c r="D34" s="0">
+        <v>568091.65864855773</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0">
+        <v>33</v>
+      </c>
+      <c r="B35" s="0">
+        <v>819.87250045741791</v>
+      </c>
+      <c r="C35" s="0">
+        <v>706.29791871824091</v>
+      </c>
+      <c r="D35" s="0">
+        <v>579074.24068739428</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0">
+        <v>34</v>
+      </c>
+      <c r="B36" s="0">
+        <v>825.05992458736637</v>
+      </c>
+      <c r="C36" s="0">
+        <v>715.21772544537669</v>
+      </c>
+      <c r="D36" s="0">
+        <v>590097.48261951015</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0">
+        <v>35</v>
+      </c>
+      <c r="B37" s="0">
+        <v>830.351083056721</v>
+      </c>
+      <c r="C37" s="0">
+        <v>723.98116758366609</v>
+      </c>
+      <c r="D37" s="0">
+        <v>601158.5466157666</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0">
+        <v>36</v>
+      </c>
+      <c r="B38" s="0">
+        <v>835.74430089973657</v>
+      </c>
+      <c r="C38" s="0">
+        <v>732.58571697046159</v>
+      </c>
+      <c r="D38" s="0">
+        <v>612254.33787861071</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0">
+        <v>37</v>
+      </c>
+      <c r="B39" s="0">
+        <v>841.23788937557777</v>
+      </c>
+      <c r="C39" s="0">
+        <v>741.02880673323364</v>
+      </c>
+      <c r="D39" s="0">
+        <v>623381.50934276835</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0">
+        <v>38</v>
+      </c>
+      <c r="B40" s="0">
+        <v>846.83014482810449</v>
+      </c>
+      <c r="C40" s="0">
+        <v>749.30783903385714</v>
+      </c>
+      <c r="D40" s="0">
+        <v>634536.46584987524</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0">
+        <v>39</v>
+      </c>
+      <c r="B41" s="0">
+        <v>852.51934776469898</v>
+      </c>
+      <c r="C41" s="0">
+        <v>757.42019180952423</v>
+      </c>
+      <c r="D41" s="0">
+        <v>645715.36790526879</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0">
+        <v>40</v>
+      </c>
+      <c r="B42" s="0">
+        <v>858.30376212375108</v>
+      </c>
+      <c r="C42" s="0">
+        <v>765.36322464721445</v>
+      </c>
+      <c r="D42" s="0">
+        <v>656914.13510586985</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0">
+        <v>41</v>
+      </c>
+      <c r="B43" s="0">
+        <v>864.1816347052827</v>
+      </c>
+      <c r="C43" s="0">
+        <v>773.13428390569334</v>
+      </c>
+      <c r="D43" s="0">
+        <v>668128.44931232021</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0">
+        <v>42</v>
+      </c>
+      <c r="B44" s="0">
+        <v>870.15119474320954</v>
+      </c>
+      <c r="C44" s="0">
+        <v>780.73070718000383</v>
+      </c>
+      <c r="D44" s="0">
+        <v>679353.75762539124</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0">
+        <v>43</v>
+      </c>
+      <c r="B45" s="0">
+        <v>876.21065360101466</v>
+      </c>
+      <c r="C45" s="0">
+        <v>788.14982718785143</v>
+      </c>
+      <c r="D45" s="0">
+        <v>690585.2752157941</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0">
+        <v>44</v>
+      </c>
+      <c r="B46" s="0">
+        <v>882.35820457536556</v>
+      </c>
+      <c r="C46" s="0">
+        <v>795.38897514426435</v>
+      </c>
+      <c r="D46" s="0">
+        <v>701817.9880473332</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0">
+        <v>45</v>
+      </c>
+      <c r="B47" s="0">
+        <v>888.59202279444366</v>
+      </c>
+      <c r="C47" s="0">
+        <v>802.44548368011761</v>
+      </c>
+      <c r="D47" s="0">
+        <v>713046.65552558145</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0">
+        <v>46</v>
+      </c>
+      <c r="B48" s="0">
+        <v>894.91026519967011</v>
+      </c>
+      <c r="C48" s="0">
+        <v>809.31668935098264</v>
+      </c>
+      <c r="D48" s="0">
+        <v>724265.81309760688</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0">
+        <v>47</v>
+      </c>
+      <c r="B49" s="0">
+        <v>901.31107060107342</v>
+      </c>
+      <c r="C49" s="0">
+        <v>815.99993477511703</v>
+      </c>
+      <c r="D49" s="0">
+        <v>735469.77482256678</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0">
+        <v>48</v>
+      </c>
+      <c r="B50" s="0">
+        <v>907.79255979787149</v>
+      </c>
+      <c r="C50" s="0">
+        <v>822.49257043285525</v>
+      </c>
+      <c r="D50" s="0">
+        <v>746652.63592797273</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0">
+        <v>49</v>
+      </c>
+      <c r="B51" s="0">
+        <v>914.3528357569561</v>
+      </c>
+      <c r="C51" s="0">
+        <v>828.79195615409037</v>
+      </c>
+      <c r="D51" s="0">
+        <v>757808.27536204737</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0">
+        <v>50</v>
+      </c>
+      <c r="B52" s="0">
+        <v>920.9899838428878</v>
+      </c>
+      <c r="C52" s="0">
+        <v>834.89546231570591</v>
+      </c>
+      <c r="D52" s="0">
+        <v>768930.35834864236</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0">
+        <v>51</v>
+      </c>
+      <c r="B53" s="0">
+        <v>927.70207209381135</v>
+      </c>
+      <c r="C53" s="0">
+        <v>840.80047076662083</v>
+      </c>
+      <c r="D53" s="0">
+        <v>780012.3389476462</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0">
+        <v>52</v>
+      </c>
+      <c r="B54" s="0">
+        <v>934.48715153834337</v>
+      </c>
+      <c r="C54" s="0">
+        <v>846.5043754944295</v>
+      </c>
+      <c r="D54" s="0">
+        <v>791047.46262053365</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0">
+        <v>53</v>
+      </c>
+      <c r="B55" s="0">
+        <v>941.3432565490549</v>
+      </c>
+      <c r="C55" s="0">
+        <v>852.00458304433118</v>
+      </c>
+      <c r="D55" s="0">
+        <v>802028.76879767038</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0">
+        <v>54</v>
+      </c>
+      <c r="B56" s="0">
+        <v>948.26840522862654</v>
+      </c>
+      <c r="C56" s="0">
+        <v>857.29851269811059</v>
+      </c>
+      <c r="D56" s="0">
+        <v>812949.0934411108</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0">
+        <v>55</v>
+      </c>
+      <c r="B57" s="0">
+        <v>955.26059982514153</v>
+      </c>
+      <c r="C57" s="0">
+        <v>862.38359641822478</v>
+      </c>
+      <c r="D57" s="0">
+        <v>823801.07159383618</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0">
+        <v>56</v>
+      </c>
+      <c r="B58" s="0">
+        <v>962.31782717330452</v>
+      </c>
+      <c r="C58" s="0">
+        <v>867.25727855958826</v>
+      </c>
+      <c r="D58" s="0">
+        <v>834577.13990369625</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0">
+        <v>57</v>
+      </c>
+      <c r="B59" s="0">
+        <v>969.43805915862981</v>
+      </c>
+      <c r="C59" s="0">
+        <v>871.91701534928131</v>
+      </c>
+      <c r="D59" s="0">
+        <v>845269.53910759254</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0">
+        <v>58</v>
+      </c>
+      <c r="B60" s="0">
+        <v>976.61925320185651</v>
+      </c>
+      <c r="C60" s="0">
+        <v>876.36027413219654</v>
+      </c>
+      <c r="D60" s="0">
+        <v>855870.31645876006</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0">
+        <v>59</v>
+      </c>
+      <c r="B61" s="0">
+        <v>983.8593527609936</v>
+      </c>
+      <c r="C61" s="0">
+        <v>880.58453237843389</v>
+      </c>
+      <c r="D61" s="0">
+        <v>866371.32807718823</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0">
+        <v>60</v>
+      </c>
+      <c r="B62" s="0">
+        <v>991.15628784853254</v>
+      </c>
+      <c r="C62" s="0">
+        <v>884.58727644612145</v>
+      </c>
+      <c r="D62" s="0">
+        <v>876764.24120038143</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0">
+        <v>61</v>
+      </c>
+      <c r="B63" s="0">
+        <v>998.50797556141856</v>
+      </c>
+      <c r="C63" s="0">
+        <v>888.36600009113943</v>
+      </c>
+      <c r="D63" s="0">
+        <v>887040.53630859859</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0">
+        <v>62</v>
+      </c>
+      <c r="B64" s="0">
+        <v>1005.9123206214185</v>
+      </c>
+      <c r="C64" s="0">
+        <v>891.91820271301162</v>
+      </c>
+      <c r="D64" s="0">
+        <v>897191.50909553026</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0">
+        <v>63</v>
+      </c>
+      <c r="B65" s="0">
+        <v>1013.3672159235135</v>
+      </c>
+      <c r="C65" s="0">
+        <v>895.24138732391793</v>
+      </c>
+      <c r="D65" s="0">
+        <v>907208.27225194254</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0">
+        <v>64</v>
+      </c>
+      <c r="B66" s="0">
+        <v>1020.870543089895</v>
+      </c>
+      <c r="C66" s="0">
+        <v>898.33305822531008</v>
+      </c>
+      <c r="D66" s="0">
+        <v>917081.75702607865</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0">
+        <v>65</v>
+      </c>
+      <c r="B67" s="0">
+        <v>1028.4201730270577</v>
+      </c>
+      <c r="C67" s="0">
+        <v>901.19071837403908</v>
+      </c>
+      <c r="D67" s="0">
+        <v>926802.71452060773</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0">
+        <v>66</v>
+      </c>
+      <c r="B68" s="0">
+        <v>1036.0139664833525</v>
+      </c>
+      <c r="C68" s="0">
+        <v>903.81186641706233</v>
+      </c>
+      <c r="D68" s="0">
+        <v>936361.71668146271</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0">
+        <v>67</v>
+      </c>
+      <c r="B69" s="0">
+        <v>1043.6497746041846</v>
+      </c>
+      <c r="C69" s="0">
+        <v>906.19399337074049</v>
+      </c>
+      <c r="D69" s="0">
+        <v>945749.15692903928</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0">
+        <v>68</v>
+      </c>
+      <c r="B70" s="0">
+        <v>1051.3254394818043</v>
+      </c>
+      <c r="C70" s="0">
+        <v>908.33457891736532</v>
+      </c>
+      <c r="D70" s="0">
+        <v>954955.25037681882</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0">
+        <v>69</v>
+      </c>
+      <c r="B71" s="0">
+        <v>1059.0387946963567</v>
+      </c>
+      <c r="C71" s="0">
+        <v>910.23108728783029</v>
+      </c>
+      <c r="D71" s="0">
+        <v>963970.03357645811</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0">
+        <v>70</v>
+      </c>
+      <c r="B72" s="0">
+        <v>1066.7876658444998</v>
+      </c>
+      <c r="C72" s="0">
+        <v>911.88096269521088</v>
+      </c>
+      <c r="D72" s="0">
+        <v>972783.36372165941</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0">
+        <v>71</v>
+      </c>
+      <c r="B73" s="0">
+        <v>1074.5698710514598</v>
+      </c>
+      <c r="C73" s="0">
+        <v>913.28162427935149</v>
+      </c>
+      <c r="D73" s="0">
+        <v>981384.91723553045</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0">
+        <v>72</v>
+      </c>
+      <c r="B74" s="0">
+        <v>1082.383221461896</v>
+      </c>
+      <c r="C74" s="0">
+        <v>914.43046051738224</v>
+      </c>
+      <c r="D74" s="0">
+        <v>989764.18765768933</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0">
+        <v>73</v>
+      </c>
+      <c r="B75" s="0">
+        <v>1090.2255217043005</v>
+      </c>
+      <c r="C75" s="0">
+        <v>915.32482304910855</v>
+      </c>
+      <c r="D75" s="0">
+        <v>997910.48273761093</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0">
+        <v>74</v>
+      </c>
+      <c r="B76" s="0">
+        <v>1098.0945703229413</v>
+      </c>
+      <c r="C76" s="0">
+        <v>915.96201985962171</v>
+      </c>
+      <c r="D76" s="0">
+        <v>1005812.9206298847</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0">
+        <v>75</v>
+      </c>
+      <c r="B77" s="0">
+        <v>1105.9881601704744</v>
+      </c>
+      <c r="C77" s="0">
+        <v>916.33930775375109</v>
+      </c>
+      <c r="D77" s="0">
+        <v>1013460.4250744573</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0">
+        <v>76</v>
+      </c>
+      <c r="B78" s="0">
+        <v>1113.9040787532963</v>
+      </c>
+      <c r="C78" s="0">
+        <v>916.4538840483799</v>
+      </c>
+      <c r="D78" s="0">
+        <v>1020841.7194307909</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0">
+        <v>77</v>
+      </c>
+      <c r="B79" s="0">
+        <v>1121.8401085204807</v>
+      </c>
+      <c r="C79" s="0">
+        <v>916.30287739861546</v>
+      </c>
+      <c r="D79" s="0">
+        <v>1027945.3194184916</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0">
+        <v>78</v>
+      </c>
+      <c r="B80" s="0">
+        <v>1129.7940270856611</v>
+      </c>
+      <c r="C80" s="0">
+        <v>915.88333766238429</v>
+      </c>
+      <c r="D80" s="0">
+        <v>1034759.5243982415</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0">
+        <v>79</v>
+      </c>
+      <c r="B81" s="0">
+        <v>1137.7636073694694</v>
+      </c>
+      <c r="C81" s="0">
+        <v>915.19222469480542</v>
+      </c>
+      <c r="D81" s="0">
+        <v>1041272.4070052517</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0">
+        <v>80</v>
+      </c>
+      <c r="B82" s="0">
+        <v>1145.7466176480414</v>
+      </c>
+      <c r="C82" s="0">
+        <v>914.22639594845941</v>
+      </c>
+      <c r="D82" s="0">
+        <v>1047471.8009225064</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0">
+        <v>81</v>
+      </c>
+      <c r="B83" s="0">
+        <v>1153.740821490612</v>
+      </c>
+      <c r="C83" s="0">
+        <v>912.98259273794361</v>
+      </c>
+      <c r="D83" s="0">
+        <v>1053345.2865521039</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="0">
+        <v>82</v>
+      </c>
+      <c r="B84" s="0">
+        <v>1161.7439775662119</v>
+      </c>
+      <c r="C84" s="0">
+        <v>911.45742500653819</v>
+      </c>
+      <c r="D84" s="0">
+        <v>1058880.1743093529</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="0">
+        <v>83</v>
+      </c>
+      <c r="B85" s="0">
+        <v>1169.7538392959179</v>
+      </c>
+      <c r="C85" s="0">
+        <v>909.64735440878724</v>
+      </c>
+      <c r="D85" s="0">
+        <v>1064063.4852250535</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="0">
+        <v>84</v>
+      </c>
+      <c r="B86" s="0">
+        <v>1177.7681543227629</v>
+      </c>
+      <c r="C86" s="0">
+        <v>907.54867549466906</v>
+      </c>
+      <c r="D86" s="0">
+        <v>1068881.9284954246</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="0">
+        <v>85</v>
+      </c>
+      <c r="B87" s="0">
+        <v>1185.7846637662365</v>
+      </c>
+      <c r="C87" s="0">
+        <v>905.15749474800464</v>
+      </c>
+      <c r="D87" s="0">
+        <v>1073321.8755652516</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="0">
+        <v>86</v>
+      </c>
+      <c r="B88" s="0">
+        <v>1193.8011012219904</v>
+      </c>
+      <c r="C88" s="0">
+        <v>902.46970719286651</v>
+      </c>
+      <c r="D88" s="0">
+        <v>1077369.3302663313</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="0">
+        <v>87</v>
+      </c>
+      <c r="B89" s="0">
+        <v>1201.8151914597477</v>
+      </c>
+      <c r="C89" s="0">
+        <v>899.48097023566174</v>
+      </c>
+      <c r="D89" s="0">
+        <v>1081009.8944581715</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0">
+        <v>88</v>
+      </c>
+      <c r="B90" s="0">
+        <v>1209.8246487631116</v>
+      </c>
+      <c r="C90" s="0">
+        <v>896.18667435599798</v>
+      </c>
+      <c r="D90" s="0">
+        <v>1084228.7285289264</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0">
+        <v>89</v>
+      </c>
+      <c r="B91" s="0">
+        <v>1217.8271748436052</v>
+      </c>
+      <c r="C91" s="0">
+        <v>892.58191019429955</v>
+      </c>
+      <c r="D91" s="0">
+        <v>1087010.5060084325</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0">
+        <v>90</v>
+      </c>
+      <c r="B92" s="0">
+        <v>1225.8204562473786</v>
+      </c>
+      <c r="C92" s="0">
+        <v>888.66143150626897</v>
+      </c>
+      <c r="D92" s="0">
+        <v>1089339.3614184633</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="0">
+        <v>91</v>
+      </c>
+      <c r="B93" s="0">
+        <v>1238.5561966693658</v>
+      </c>
+      <c r="C93" s="0">
+        <v>884.41961336075542</v>
+      </c>
+      <c r="D93" s="0">
+        <v>1095403.3925838883</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0">
+        <v>92</v>
+      </c>
+      <c r="B94" s="0">
+        <v>1251.2765583621394</v>
+      </c>
+      <c r="C94" s="0">
+        <v>879.85040484468834</v>
+      </c>
+      <c r="D94" s="0">
+        <v>1100936.1864475966</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0">
+        <v>93</v>
+      </c>
+      <c r="B95" s="0">
+        <v>1263.9777124453376</v>
+      </c>
+      <c r="C95" s="0">
+        <v>874.94727540188569</v>
+      </c>
+      <c r="D95" s="0">
+        <v>1105913.8556727562</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0">
+        <v>94</v>
+      </c>
+      <c r="B96" s="0">
+        <v>1276.6557979843985</v>
+      </c>
+      <c r="C96" s="0">
+        <v>869.70315376590042</v>
+      </c>
+      <c r="D96" s="0">
+        <v>1110311.5737805536</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0">
+        <v>95</v>
+      </c>
+      <c r="B97" s="0">
+        <v>1289.3069153111589</v>
+      </c>
+      <c r="C97" s="0">
+        <v>864.11035824295891</v>
+      </c>
+      <c r="D97" s="0">
+        <v>1114103.4604746499</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0">
+        <v>96</v>
+      </c>
+      <c r="B98" s="0">
+        <v>1301.927117800635</v>
+      </c>
+      <c r="C98" s="0">
+        <v>858.16051684984927</v>
+      </c>
+      <c r="D98" s="0">
+        <v>1117262.4483126274</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0">
+        <v>97</v>
+      </c>
+      <c r="B99" s="0">
+        <v>1314.5124017661517</v>
+      </c>
+      <c r="C99" s="0">
+        <v>851.84447550063726</v>
+      </c>
+      <c r="D99" s="0">
+        <v>1119760.1274215705</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="0">
+        <v>98</v>
+      </c>
+      <c r="B100" s="0">
+        <v>1327.0586940512151</v>
+      </c>
+      <c r="C100" s="0">
+        <v>845.152192048703</v>
+      </c>
+      <c r="D100" s="0">
+        <v>1121566.5642546734</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0">
+        <v>99</v>
+      </c>
+      <c r="B101" s="0">
+        <v>1339.5618367891709</v>
+      </c>
+      <c r="C101" s="0">
+        <v>838.07261350497902</v>
+      </c>
+      <c r="D101" s="0">
+        <v>1122650.0895094306</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="0">
+        <v>100</v>
+      </c>
+      <c r="B102" s="0">
+        <v>1352.0175686629702</v>
+      </c>
+      <c r="C102" s="0">
+        <v>830.59353314043449</v>
+      </c>
+      <c r="D102" s="0">
+        <v>1122977.0492237164</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="0">
+        <v>101</v>
+      </c>
+      <c r="B103" s="0">
+        <v>1364.4215018170962</v>
+      </c>
+      <c r="C103" s="0">
+        <v>822.70142340150016</v>
+      </c>
+      <c r="D103" s="0">
+        <v>1122511.5116645377</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="0">
+        <v>102</v>
+      </c>
+      <c r="B104" s="0">
+        <v>1376.7690933374222</v>
+      </c>
+      <c r="C104" s="0">
+        <v>814.38123956864365</v>
+      </c>
+      <c r="D104" s="0">
+        <v>1121214.9208319276</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="0">
+        <v>103</v>
+      </c>
+      <c r="B105" s="0">
+        <v>1389.0556099027131</v>
+      </c>
+      <c r="C105" s="0">
+        <v>805.61618779807202</v>
+      </c>
+      <c r="D105" s="0">
+        <v>1119045.6850893495</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="0">
+        <v>104</v>
+      </c>
+      <c r="B106" s="0">
+        <v>1401.2760837956632</v>
+      </c>
+      <c r="C106" s="0">
+        <v>796.3874495043633</v>
+      </c>
+      <c r="D106" s="0">
+        <v>1115958.6864254908</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="0">
+        <v>105</v>
+      </c>
+      <c r="B107" s="0">
+        <v>1413.4252579020172</v>
+      </c>
+      <c r="C107" s="0">
+        <v>786.67385182756288</v>
+      </c>
+      <c r="D107" s="0">
+        <v>1111904.6919041462</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="0">
+        <v>106</v>
+      </c>
+      <c r="B108" s="0">
+        <v>1425.4975165663791</v>
+      </c>
+      <c r="C108" s="0">
+        <v>776.45147098271252</v>
+      </c>
+      <c r="D108" s="0">
+        <v>1106829.6436201686</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="0">
+        <v>107</v>
+      </c>
+      <c r="B109" s="0">
+        <v>1437.4867981291952</v>
+      </c>
+      <c r="C109" s="0">
+        <v>765.69315132751422</v>
+      </c>
+      <c r="D109" s="0">
+        <v>1100673.7964512417</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="0">
+        <v>108</v>
+      </c>
+      <c r="B110" s="0">
+        <v>1449.3864835178456</v>
+      </c>
+      <c r="C110" s="0">
+        <v>754.36791758760956</v>
+      </c>
+      <c r="D110" s="0">
+        <v>1093370.6633509854</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="0">
+        <v>109</v>
+      </c>
+      <c r="B111" s="0">
+        <v>1461.1892532201875</v>
+      </c>
+      <c r="C111" s="0">
+        <v>742.4402502316309</v>
+      </c>
+      <c r="D111" s="0">
+        <v>1084845.7147965659</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="0">
+        <v>110</v>
+      </c>
+      <c r="B112" s="0">
+        <v>1472.8869020475863</v>
+      </c>
+      <c r="C112" s="0">
+        <v>729.86918355829118</v>
+      </c>
+      <c r="D112" s="0">
+        <v>1075014.7606711725</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0">
+        <v>111</v>
+      </c>
+      <c r="B113" s="0">
+        <v>1484.4700968546435</v>
+      </c>
+      <c r="C113" s="0">
+        <v>716.60717121468474</v>
+      </c>
+      <c r="D113" s="0">
+        <v>1063781.9168597951</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0">
+        <v>112</v>
+      </c>
+      <c r="B114" s="0">
+        <v>1495.928056121586</v>
+      </c>
+      <c r="C114" s="0">
+        <v>702.59864236294152</v>
+      </c>
+      <c r="D114" s="0">
+        <v>1051037.0213036605</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="0">
+        <v>113</v>
+      </c>
+      <c r="B115" s="0">
+        <v>1507.2481208790759</v>
+      </c>
+      <c r="C115" s="0">
+        <v>687.77813994487747</v>
+      </c>
+      <c r="D115" s="0">
+        <v>1036652.3090136227</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="0">
+        <v>114</v>
+      </c>
+      <c r="B116" s="0">
+        <v>1518.4151719554291</v>
+      </c>
+      <c r="C116" s="0">
+        <v>672.06788451712623</v>
+      </c>
+      <c r="D116" s="0">
+        <v>1020478.0724347937</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="0">
+        <v>115</v>
+      </c>
+      <c r="B117" s="0">
+        <v>1529.4108256751295</v>
+      </c>
+      <c r="C117" s="0">
+        <v>655.3745328594913</v>
+      </c>
+      <c r="D117" s="0">
+        <v>1002336.9054270869</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="0">
+        <v>116</v>
+      </c>
+      <c r="B118" s="0">
+        <v>1540.2123031229089</v>
+      </c>
+      <c r="C118" s="0">
+        <v>637.58478232816469</v>
+      </c>
+      <c r="D118" s="0">
+        <v>982015.92602578108</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="0">
+        <v>117</v>
+      </c>
+      <c r="B119" s="0">
+        <v>1550.7908062190513</v>
+      </c>
+      <c r="C119" s="0">
+        <v>618.55927760888369</v>
+      </c>
+      <c r="D119" s="0">
+        <v>959256.04081735469</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="0">
+        <v>118</v>
+      </c>
+      <c r="B120" s="0">
+        <v>1561.1091266248409</v>
+      </c>
+      <c r="C120" s="0">
+        <v>598.12394519421275</v>
+      </c>
+      <c r="D120" s="0">
+        <v>933736.74969554169</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="0">
+        <v>119</v>
+      </c>
+      <c r="B121" s="0">
+        <v>1571.1180196247708</v>
+      </c>
+      <c r="C121" s="0">
+        <v>576.05729119978446</v>
+      </c>
+      <c r="D121" s="0">
+        <v>905053.99054021528</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="0">
         <v>120</v>
       </c>
-      <c r="B26" s="0">
+      <c r="B122" s="0">
         <v>1580.75050658341</v>
       </c>
-      <c r="C26" s="0">
+      <c r="C122" s="0">
         <v>552.07109398706075</v>
       </c>
-      <c r="D26" s="0">
+      <c r="D122" s="0">
         <v>872686.6614901037</v>
       </c>
     </row>
@@ -450,7 +1794,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.42578125" customWidth="true"/>
@@ -489,337 +1833,1681 @@
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B3" s="0">
-        <v>836.24929120518345</v>
+        <v>832.3978308723739</v>
       </c>
       <c r="C3" s="0">
-        <v>240.78935819092459</v>
+        <v>166.80137021226523</v>
       </c>
       <c r="D3" s="0">
-        <v>201359.93011691171</v>
+        <v>138845.09875122938</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B4" s="0">
-        <v>845.49858312141623</v>
+        <v>832.9328631788178</v>
       </c>
       <c r="C4" s="0">
-        <v>309.75261914314609</v>
+        <v>189.2533255534585</v>
       </c>
       <c r="D4" s="0">
-        <v>261895.4006036777</v>
+        <v>157635.31431935509</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B5" s="0">
-        <v>858.4401461782328</v>
+        <v>833.80028693010718</v>
       </c>
       <c r="C5" s="0">
-        <v>370.74467979663336</v>
+        <v>208.13588000201366</v>
       </c>
       <c r="D5" s="0">
-        <v>318262.11711942405</v>
+        <v>173543.75646612936</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B6" s="0">
-        <v>874.67903719724472</v>
+        <v>834.91882830458189</v>
       </c>
       <c r="C6" s="0">
-        <v>427.15835056453733</v>
+        <v>225.0812062648838</v>
       </c>
       <c r="D6" s="0">
-        <v>373626.45480255265</v>
+        <v>187924.53700805872</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B7" s="0">
-        <v>893.98616237047918</v>
+        <v>836.24929120518345</v>
       </c>
       <c r="C7" s="0">
-        <v>479.8175876563248</v>
+        <v>240.78935819092459</v>
       </c>
       <c r="D7" s="0">
-        <v>428950.28382673883</v>
+        <v>201359.93011691171</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="B8" s="0">
-        <v>916.16847861785027</v>
+        <v>837.76882467119708</v>
       </c>
       <c r="C8" s="0">
-        <v>528.8351082637148</v>
+        <v>255.63104201426881</v>
       </c>
       <c r="D8" s="0">
-        <v>484502.05657767371</v>
+        <v>214159.7176177674</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="B9" s="0">
-        <v>941.03491745786221</v>
+        <v>839.46259371732504</v>
       </c>
       <c r="C9" s="0">
-        <v>574.06214941368796</v>
+        <v>269.82722722924746</v>
       </c>
       <c r="D9" s="0">
-        <v>540212.52738919284</v>
+        <v>226509.86402541809</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="B10" s="0">
-        <v>968.38498361179211</v>
+        <v>841.32025204251022</v>
       </c>
       <c r="C10" s="0">
-        <v>615.24156528877461</v>
+        <v>283.52004841820894</v>
       </c>
       <c r="D10" s="0">
-        <v>595790.69311946328</v>
+        <v>238531.15859431226</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="B11" s="0">
-        <v>998.00473693582944</v>
+        <v>843.33419256281923</v>
       </c>
       <c r="C11" s="0">
-        <v>652.07090510774265</v>
+        <v>296.80588179582861</v>
       </c>
       <c r="D11" s="0">
-        <v>650769.85211556091</v>
+        <v>250306.54867218068</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="B12" s="0">
-        <v>1029.665668583041</v>
+        <v>845.49858312141623</v>
       </c>
       <c r="C12" s="0">
-        <v>684.23163816716215</v>
+        <v>309.75261914314609</v>
       </c>
       <c r="D12" s="0">
-        <v>704529.82717906043</v>
+        <v>261895.4006036777</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="B13" s="0">
-        <v>1063.1248515370469</v>
+        <v>847.80879311756212</v>
       </c>
       <c r="C13" s="0">
-        <v>711.40338890365251</v>
+        <v>322.40945996738185</v>
       </c>
       <c r="D13" s="0">
-        <v>756310.62221114757</v>
+        <v>273341.57514463097</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="B14" s="0">
-        <v>1098.1256709271816</v>
+        <v>850.2610325225321</v>
       </c>
       <c r="C14" s="0">
-        <v>733.27035737934352</v>
+        <v>334.81282063635126</v>
       </c>
       <c r="D14" s="0">
-        <v>805223.00316820585</v>
+        <v>284678.29457604536</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="B15" s="0">
-        <v>1134.3987664542697</v>
+        <v>852.85211423684234</v>
       </c>
       <c r="C15" s="0">
-        <v>750.82377471453344</v>
+        <v>346.99008071142805</v>
       </c>
       <c r="D15" s="0">
-        <v>851733.56386070524</v>
+        <v>295931.223953954</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="B16" s="0">
-        <v>1171.6629202825986</v>
+        <v>855.57929194319309</v>
       </c>
       <c r="C16" s="0">
-        <v>765.73376426729487</v>
+        <v>358.96205502137445</v>
       </c>
       <c r="D16" s="0">
-        <v>897181.85840040573</v>
+        <v>307120.50086966105</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="B17" s="0">
-        <v>1209.625607514449</v>
+        <v>858.4401461782328</v>
       </c>
       <c r="C17" s="0">
-        <v>774.94579514457632</v>
+        <v>370.74467979663336</v>
       </c>
       <c r="D17" s="0">
-        <v>937394.27824252588</v>
+        <v>318262.11711942405</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="B18" s="0">
-        <v>1247.9828049298872</v>
+        <v>861.43250230325634</v>
       </c>
       <c r="C18" s="0">
-        <v>778.24507525756667</v>
+        <v>382.35019523029916</v>
       </c>
       <c r="D18" s="0">
-        <v>971236.47194280918</v>
+        <v>329368.8854333752</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="B19" s="0">
-        <v>1286.4173727909151</v>
+        <v>864.55437020991872</v>
       </c>
       <c r="C19" s="0">
-        <v>775.41778683455345</v>
+        <v>393.7879948296378</v>
       </c>
       <c r="D19" s="0">
-        <v>997510.91215505206</v>
+        <v>340451.13186616422</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="B20" s="0">
-        <v>1324.5947280552086</v>
+        <v>867.80389921293386</v>
       </c>
       <c r="C20" s="0">
-        <v>766.23335667400693</v>
+        <v>405.06524812158278</v>
       </c>
       <c r="D20" s="0">
-        <v>1014948.6647104359</v>
+        <v>351517.20175556408</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="B21" s="0">
-        <v>1385.8944483759385</v>
+        <v>871.17934378730252</v>
       </c>
       <c r="C21" s="0">
-        <v>750.41426091137441</v>
+        <v>416.18736546795492</v>
       </c>
       <c r="D21" s="0">
-        <v>1039994.9581792068</v>
+        <v>362573.8359409392</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="B22" s="0">
-        <v>1445.9853774056996</v>
+        <v>874.67903719724472</v>
       </c>
       <c r="C22" s="0">
-        <v>727.58272619971535</v>
+        <v>427.15835056453733</v>
       </c>
       <c r="D22" s="0">
-        <v>1052073.9829377632</v>
+        <v>373626.45480255265</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="B23" s="0">
-        <v>1504.1865450010093</v>
+        <v>878.30137096458009</v>
       </c>
       <c r="C23" s="0">
-        <v>697.16094635783361</v>
+        <v>437.98107155539867</v>
       </c>
       <c r="D23" s="0">
-        <v>1048660.1152116237</v>
+        <v>384679.37560364249</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0">
-        <v>110</v>
+        <v>22</v>
       </c>
       <c r="B24" s="0">
-        <v>1559.6227044165041</v>
+        <v>882.04477872241625</v>
       </c>
       <c r="C24" s="0">
-        <v>658.16769180109384</v>
+        <v>448.65747219959906</v>
       </c>
       <c r="D24" s="0">
-        <v>1026493.2754463902</v>
+        <v>395735.98078845395</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>115</v>
+        <v>23</v>
       </c>
       <c r="B25" s="0">
-        <v>1610.9512582816076</v>
+        <v>885.90772340606566</v>
       </c>
       <c r="C25" s="0">
-        <v>608.74958206735619</v>
+        <v>459.18873822687573</v>
       </c>
       <c r="D25" s="0">
-        <v>980665.90520981024</v>
+        <v>406798.84969627531</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0">
+        <v>24</v>
+      </c>
+      <c r="B26" s="0">
+        <v>889.88868701411684</v>
+      </c>
+      <c r="C26" s="0">
+        <v>469.57542975015969</v>
+      </c>
+      <c r="D26" s="0">
+        <v>417869.86263445928</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0">
+        <v>25</v>
+      </c>
+      <c r="B27" s="0">
+        <v>893.98616237047918</v>
+      </c>
+      <c r="C27" s="0">
+        <v>479.8175876563248</v>
+      </c>
+      <c r="D27" s="0">
+        <v>428950.28382673883</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0">
+        <v>26</v>
+      </c>
+      <c r="B28" s="0">
+        <v>898.19864645976918</v>
+      </c>
+      <c r="C28" s="0">
+        <v>489.91481982831675</v>
+      </c>
+      <c r="D28" s="0">
+        <v>440040.8280503758</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0">
+        <v>27</v>
+      </c>
+      <c r="B29" s="0">
+        <v>902.52463501107718</v>
+      </c>
+      <c r="C29" s="0">
+        <v>499.86637157754262</v>
+      </c>
+      <c r="D29" s="0">
+        <v>451141.71456233313</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0">
+        <v>28</v>
+      </c>
+      <c r="B30" s="0">
+        <v>906.96261808061843</v>
+      </c>
+      <c r="C30" s="0">
+        <v>509.67118359997994</v>
+      </c>
+      <c r="D30" s="0">
+        <v>462252.71103808534</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0">
+        <v>29</v>
+      </c>
+      <c r="B31" s="0">
+        <v>911.51107643985631</v>
+      </c>
+      <c r="C31" s="0">
+        <v>519.32793998944283</v>
+      </c>
+      <c r="D31" s="0">
+        <v>473373.16960507014</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0">
+        <v>30</v>
+      </c>
+      <c r="B32" s="0">
+        <v>916.16847861785027</v>
+      </c>
+      <c r="C32" s="0">
+        <v>528.8351082637148</v>
+      </c>
+      <c r="D32" s="0">
+        <v>484502.05657767371</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0">
+        <v>31</v>
+      </c>
+      <c r="B33" s="0">
+        <v>920.93327847857029</v>
+      </c>
+      <c r="C33" s="0">
+        <v>538.19097292673985</v>
+      </c>
+      <c r="D33" s="0">
+        <v>495637.97714499402</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0">
+        <v>32</v>
+      </c>
+      <c r="B34" s="0">
+        <v>925.80391323843151</v>
+      </c>
+      <c r="C34" s="0">
+        <v>547.3936637628467</v>
+      </c>
+      <c r="D34" s="0">
+        <v>506779.19599356566</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0">
+        <v>33</v>
+      </c>
+      <c r="B35" s="0">
+        <v>930.77880184822288</v>
+      </c>
+      <c r="C35" s="0">
+        <v>556.44117980931992</v>
+      </c>
+      <c r="D35" s="0">
+        <v>517923.65464193036</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0">
+        <v>34</v>
+      </c>
+      <c r="B36" s="0">
+        <v>935.85634367835098</v>
+      </c>
+      <c r="C36" s="0">
+        <v>565.33140976129607</v>
+      </c>
+      <c r="D36" s="0">
+        <v>529068.98610573413</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0">
+        <v>35</v>
+      </c>
+      <c r="B37" s="0">
+        <v>941.03491745786221</v>
+      </c>
+      <c r="C37" s="0">
+        <v>574.06214941368796</v>
+      </c>
+      <c r="D37" s="0">
+        <v>540212.52738919284</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0">
+        <v>36</v>
+      </c>
+      <c r="B38" s="0">
+        <v>946.31288042683229</v>
+      </c>
+      <c r="C38" s="0">
+        <v>582.63111662808331</v>
+      </c>
+      <c r="D38" s="0">
+        <v>551351.33020262316</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0">
+        <v>37</v>
+      </c>
+      <c r="B39" s="0">
+        <v>951.68856766896874</v>
+      </c>
+      <c r="C39" s="0">
+        <v>591.03596422056717</v>
+      </c>
+      <c r="D39" s="0">
+        <v>562482.17022991937</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0">
+        <v>38</v>
+      </c>
+      <c r="B40" s="0">
+        <v>957.16029159704124</v>
+      </c>
+      <c r="C40" s="0">
+        <v>599.27429109341585</v>
+      </c>
+      <c r="D40" s="0">
+        <v>573601.55520958407</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0">
+        <v>39</v>
+      </c>
+      <c r="B41" s="0">
+        <v>962.72634156842582</v>
+      </c>
+      <c r="C41" s="0">
+        <v>607.34365187542983</v>
+      </c>
+      <c r="D41" s="0">
+        <v>584705.73204484012</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0">
+        <v>40</v>
+      </c>
+      <c r="B42" s="0">
+        <v>968.38498361179211</v>
+      </c>
+      <c r="C42" s="0">
+        <v>615.24156528877461</v>
+      </c>
+      <c r="D42" s="0">
+        <v>595790.69311946328</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0">
+        <v>41</v>
+      </c>
+      <c r="B43" s="0">
+        <v>974.13446024901305</v>
+      </c>
+      <c r="C43" s="0">
+        <v>622.96552142252335</v>
+      </c>
+      <c r="D43" s="0">
+        <v>606852.18196467473</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0">
+        <v>42</v>
+      </c>
+      <c r="B44" s="0">
+        <v>979.97299039884979</v>
+      </c>
+      <c r="C44" s="0">
+        <v>630.51298806227078</v>
+      </c>
+      <c r="D44" s="0">
+        <v>617885.69839669776</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0">
+        <v>43</v>
+      </c>
+      <c r="B45" s="0">
+        <v>985.89876935100142</v>
+      </c>
+      <c r="C45" s="0">
+        <v>637.88141620017495</v>
+      </c>
+      <c r="D45" s="0">
+        <v>628886.50322362641</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0">
+        <v>44</v>
+      </c>
+      <c r="B46" s="0">
+        <v>991.90996880075238</v>
+      </c>
+      <c r="C46" s="0">
+        <v>645.06824482912305</v>
+      </c>
+      <c r="D46" s="0">
+        <v>639849.62260281155</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0">
+        <v>45</v>
+      </c>
+      <c r="B47" s="0">
+        <v>998.00473693582944</v>
+      </c>
+      <c r="C47" s="0">
+        <v>652.07090510774265</v>
+      </c>
+      <c r="D47" s="0">
+        <v>650769.85211556091</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0">
+        <v>46</v>
+      </c>
+      <c r="B48" s="0">
+        <v>1004.1811985681927</v>
+      </c>
+      <c r="C48" s="0">
+        <v>658.88682396879949</v>
+      </c>
+      <c r="D48" s="0">
+        <v>661641.76061377884</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0">
+        <v>47</v>
+      </c>
+      <c r="B49" s="0">
+        <v>1010.4374553044056</v>
+      </c>
+      <c r="C49" s="0">
+        <v>665.51342723179391</v>
+      </c>
+      <c r="D49" s="0">
+        <v>672459.69388300751</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0">
+        <v>48</v>
+      </c>
+      <c r="B50" s="0">
+        <v>1016.7715857489953</v>
+      </c>
+      <c r="C50" s="0">
+        <v>671.94814227058907</v>
+      </c>
+      <c r="D50" s="0">
+        <v>683217.77815755841</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0">
+        <v>49</v>
+      </c>
+      <c r="B51" s="0">
+        <v>1023.1816457358286</v>
+      </c>
+      <c r="C51" s="0">
+        <v>678.18840027863587</v>
+      </c>
+      <c r="D51" s="0">
+        <v>693909.92351604358</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0">
+        <v>50</v>
+      </c>
+      <c r="B52" s="0">
+        <v>1029.665668583041</v>
+      </c>
+      <c r="C52" s="0">
+        <v>684.23163816716215</v>
+      </c>
+      <c r="D52" s="0">
+        <v>704529.82717906043</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0">
+        <v>51</v>
+      </c>
+      <c r="B53" s="0">
+        <v>1036.2216653674589</v>
+      </c>
+      <c r="C53" s="0">
+        <v>690.07530012568088</v>
+      </c>
+      <c r="D53" s="0">
+        <v>715070.97672518203</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0">
+        <v>52</v>
+      </c>
+      <c r="B54" s="0">
+        <v>1042.8476252147952</v>
+      </c>
+      <c r="C54" s="0">
+        <v>695.71683886890458</v>
+      </c>
+      <c r="D54" s="0">
+        <v>725526.65323638148</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0">
+        <v>53</v>
+      </c>
+      <c r="B55" s="0">
+        <v>1049.5415156021406</v>
+      </c>
+      <c r="C55" s="0">
+        <v>701.15371658957838</v>
+      </c>
+      <c r="D55" s="0">
+        <v>735889.93437949987</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0">
+        <v>54</v>
+      </c>
+      <c r="B56" s="0">
+        <v>1056.3012826694735</v>
+      </c>
+      <c r="C56" s="0">
+        <v>706.3834056327845</v>
+      </c>
+      <c r="D56" s="0">
+        <v>746153.69742634124</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0">
+        <v>55</v>
+      </c>
+      <c r="B57" s="0">
+        <v>1063.1248515370469</v>
+      </c>
+      <c r="C57" s="0">
+        <v>711.40338890365251</v>
+      </c>
+      <c r="D57" s="0">
+        <v>756310.62221114757</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0">
+        <v>56</v>
+      </c>
+      <c r="B58" s="0">
+        <v>1070.0101266255958</v>
+      </c>
+      <c r="C58" s="0">
+        <v>716.21116001730104</v>
+      </c>
+      <c r="D58" s="0">
+        <v>766353.19402077713</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0">
+        <v>57</v>
+      </c>
+      <c r="B59" s="0">
+        <v>1076.9549919763501</v>
+      </c>
+      <c r="C59" s="0">
+        <v>720.80422319684988</v>
+      </c>
+      <c r="D59" s="0">
+        <v>776273.70640948275</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0">
+        <v>58</v>
+      </c>
+      <c r="B60" s="0">
+        <v>1083.9573115678334</v>
+      </c>
+      <c r="C60" s="0">
+        <v>725.18009292271631</v>
+      </c>
+      <c r="D60" s="0">
+        <v>786064.2639270192</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0">
+        <v>59</v>
+      </c>
+      <c r="B61" s="0">
+        <v>1091.0149296263744</v>
+      </c>
+      <c r="C61" s="0">
+        <v>729.3362933338766</v>
+      </c>
+      <c r="D61" s="0">
+        <v>795716.7847456201</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0">
+        <v>60</v>
+      </c>
+      <c r="B62" s="0">
+        <v>1098.1256709271816</v>
+      </c>
+      <c r="C62" s="0">
+        <v>733.27035737934352</v>
+      </c>
+      <c r="D62" s="0">
+        <v>805223.00316820585</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0">
+        <v>61</v>
+      </c>
+      <c r="B63" s="0">
+        <v>1105.2873410826846</v>
+      </c>
+      <c r="C63" s="0">
+        <v>736.97982571582327</v>
+      </c>
+      <c r="D63" s="0">
+        <v>814574.47199702263</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0">
+        <v>62</v>
+      </c>
+      <c r="B64" s="0">
+        <v>1112.4977268146779</v>
+      </c>
+      <c r="C64" s="0">
+        <v>740.46224534517637</v>
+      </c>
+      <c r="D64" s="0">
+        <v>823762.56473860098</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0">
+        <v>63</v>
+      </c>
+      <c r="B65" s="0">
+        <v>1119.7545962065819</v>
+      </c>
+      <c r="C65" s="0">
+        <v>743.71516798299786</v>
+      </c>
+      <c r="D65" s="0">
+        <v>832778.47761751199</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0">
+        <v>64</v>
+      </c>
+      <c r="B66" s="0">
+        <v>1127.0556989318552</v>
+      </c>
+      <c r="C66" s="0">
+        <v>747.17765204300713</v>
+      </c>
+      <c r="D66" s="0">
+        <v>842110.83084959386</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0">
+        <v>65</v>
+      </c>
+      <c r="B67" s="0">
+        <v>1134.3987664542697</v>
+      </c>
+      <c r="C67" s="0">
+        <v>750.82377471453344</v>
+      </c>
+      <c r="D67" s="0">
+        <v>851733.56386070524</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0">
+        <v>66</v>
+      </c>
+      <c r="B68" s="0">
+        <v>1141.7815121953809</v>
+      </c>
+      <c r="C68" s="0">
+        <v>754.25097253329159</v>
+      </c>
+      <c r="D68" s="0">
+        <v>861189.81599389832</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0">
+        <v>67</v>
+      </c>
+      <c r="B69" s="0">
+        <v>1149.2016316640584</v>
+      </c>
+      <c r="C69" s="0">
+        <v>757.45738798545415</v>
+      </c>
+      <c r="D69" s="0">
+        <v>870471.26618887961</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0">
+        <v>68</v>
+      </c>
+      <c r="B70" s="0">
+        <v>1156.6568025424224</v>
+      </c>
+      <c r="C70" s="0">
+        <v>760.44119083556211</v>
+      </c>
+      <c r="D70" s="0">
+        <v>879569.47631341335</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0">
+        <v>69</v>
+      </c>
+      <c r="B71" s="0">
+        <v>1164.1446847219283</v>
+      </c>
+      <c r="C71" s="0">
+        <v>763.20057651010416</v>
+      </c>
+      <c r="D71" s="0">
+        <v>888475.89452094911</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0">
+        <v>70</v>
+      </c>
+      <c r="B72" s="0">
+        <v>1171.6629202825986</v>
+      </c>
+      <c r="C72" s="0">
+        <v>765.73376426729487</v>
+      </c>
+      <c r="D72" s="0">
+        <v>897181.85840040573</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0">
+        <v>71</v>
+      </c>
+      <c r="B73" s="0">
+        <v>1179.2091334076356</v>
+      </c>
+      <c r="C73" s="0">
+        <v>768.03899513633815</v>
+      </c>
+      <c r="D73" s="0">
+        <v>905678.59787799255</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0">
+        <v>72</v>
+      </c>
+      <c r="B74" s="0">
+        <v>1186.780930224641</v>
+      </c>
+      <c r="C74" s="0">
+        <v>770.11452960721306</v>
+      </c>
+      <c r="D74" s="0">
+        <v>913957.23782676016</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0">
+        <v>73</v>
+      </c>
+      <c r="B75" s="0">
+        <v>1194.3758985636114</v>
+      </c>
+      <c r="C75" s="0">
+        <v>771.95864504953272</v>
+      </c>
+      <c r="D75" s="0">
+        <v>922008.80033498362</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0">
+        <v>74</v>
+      </c>
+      <c r="B76" s="0">
+        <v>1201.9916076205984</v>
+      </c>
+      <c r="C76" s="0">
+        <v>773.56963283622235</v>
+      </c>
+      <c r="D76" s="0">
+        <v>929824.20657928695</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0">
+        <v>75</v>
+      </c>
+      <c r="B77" s="0">
+        <v>1209.625607514449</v>
+      </c>
+      <c r="C77" s="0">
+        <v>774.94579514457632</v>
+      </c>
+      <c r="D77" s="0">
+        <v>937394.27824252588</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0">
+        <v>76</v>
+      </c>
+      <c r="B78" s="0">
+        <v>1217.2754287223479</v>
+      </c>
+      <c r="C78" s="0">
+        <v>776.0854414036703</v>
+      </c>
+      <c r="D78" s="0">
+        <v>944709.73840982537</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0">
+        <v>77</v>
+      </c>
+      <c r="B79" s="0">
+        <v>1224.9385813778843</v>
+      </c>
+      <c r="C79" s="0">
+        <v>776.98688435300142</v>
+      </c>
+      <c r="D79" s="0">
+        <v>951761.21186858777</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0">
+        <v>78</v>
+      </c>
+      <c r="B80" s="0">
+        <v>1232.6125544130989</v>
+      </c>
+      <c r="C80" s="0">
+        <v>777.64843567255184</v>
+      </c>
+      <c r="D80" s="0">
+        <v>958539.22472969454</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0">
+        <v>79</v>
+      </c>
+      <c r="B81" s="0">
+        <v>1240.2948145232465</v>
+      </c>
+      <c r="C81" s="0">
+        <v>778.06840113911483</v>
+      </c>
+      <c r="D81" s="0">
+        <v>965034.20327723737</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0">
+        <v>80</v>
+      </c>
+      <c r="B82" s="0">
+        <v>1247.9828049298872</v>
+      </c>
+      <c r="C82" s="0">
+        <v>778.24507525756667</v>
+      </c>
+      <c r="D82" s="0">
+        <v>971236.47194280918</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0">
+        <v>81</v>
+      </c>
+      <c r="B83" s="0">
+        <v>1255.673943914258</v>
+      </c>
+      <c r="C83" s="0">
+        <v>778.17673530865591</v>
+      </c>
+      <c r="D83" s="0">
+        <v>977136.25028734154</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="0">
+        <v>82</v>
+      </c>
+      <c r="B84" s="0">
+        <v>1263.3656230885363</v>
+      </c>
+      <c r="C84" s="0">
+        <v>777.86163474669229</v>
+      </c>
+      <c r="D84" s="0">
+        <v>982723.6488584223</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="0">
+        <v>83</v>
+      </c>
+      <c r="B85" s="0">
+        <v>1271.0552053675442</v>
+      </c>
+      <c r="C85" s="0">
+        <v>777.29799587097614</v>
+      </c>
+      <c r="D85" s="0">
+        <v>987988.66377356416</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="0">
+        <v>84</v>
+      </c>
+      <c r="B86" s="0">
+        <v>1278.7400225974516</v>
+      </c>
+      <c r="C86" s="0">
+        <v>776.48400168375497</v>
+      </c>
+      <c r="D86" s="0">
+        <v>992921.16985964449</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="0">
+        <v>85</v>
+      </c>
+      <c r="B87" s="0">
+        <v>1286.4173727909151</v>
+      </c>
+      <c r="C87" s="0">
+        <v>775.41778683455345</v>
+      </c>
+      <c r="D87" s="0">
+        <v>997510.91215505206</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="0">
+        <v>86</v>
+      </c>
+      <c r="B88" s="0">
+        <v>1294.0845169096829</v>
+      </c>
+      <c r="C88" s="0">
+        <v>774.0974275356125</v>
+      </c>
+      <c r="D88" s="0">
+        <v>1001747.4955534514</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="0">
+        <v>87</v>
+      </c>
+      <c r="B89" s="0">
+        <v>1301.7386751256274</v>
+      </c>
+      <c r="C89" s="0">
+        <v>772.52093031539425</v>
+      </c>
+      <c r="D89" s="0">
+        <v>1005620.3723355784</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0">
+        <v>88</v>
+      </c>
+      <c r="B90" s="0">
+        <v>1309.3770224791845</v>
+      </c>
+      <c r="C90" s="0">
+        <v>770.6862194561802</v>
+      </c>
+      <c r="D90" s="0">
+        <v>1009118.8272972725</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0">
+        <v>89</v>
+      </c>
+      <c r="B91" s="0">
+        <v>1316.9966838397402</v>
+      </c>
+      <c r="C91" s="0">
+        <v>768.59112293703402</v>
+      </c>
+      <c r="D91" s="0">
+        <v>1012231.9601367358</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0">
+        <v>90</v>
+      </c>
+      <c r="B92" s="0">
+        <v>1324.5947280552086</v>
+      </c>
+      <c r="C92" s="0">
+        <v>766.23335667400693</v>
+      </c>
+      <c r="D92" s="0">
+        <v>1014948.6647104359</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="0">
+        <v>91</v>
+      </c>
+      <c r="B93" s="0">
+        <v>1336.9221966705541</v>
+      </c>
+      <c r="C93" s="0">
+        <v>763.61050681445909</v>
+      </c>
+      <c r="D93" s="0">
+        <v>1020887.8361711018</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0">
+        <v>92</v>
+      </c>
+      <c r="B94" s="0">
+        <v>1349.2205413632451</v>
+      </c>
+      <c r="C94" s="0">
+        <v>760.72000980049506</v>
+      </c>
+      <c r="D94" s="0">
+        <v>1026379.0634488771</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0">
+        <v>93</v>
+      </c>
+      <c r="B95" s="0">
+        <v>1361.4851698575653</v>
+      </c>
+      <c r="C95" s="0">
+        <v>757.55912986619842</v>
+      </c>
+      <c r="D95" s="0">
+        <v>1031405.5206030306</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0">
+        <v>94</v>
+      </c>
+      <c r="B96" s="0">
+        <v>1373.7114001374623</v>
+      </c>
+      <c r="C96" s="0">
+        <v>754.12493357267795</v>
+      </c>
+      <c r="D96" s="0">
+        <v>1035950.0183766942</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0">
+        <v>95</v>
+      </c>
+      <c r="B97" s="0">
+        <v>1385.8944483759385</v>
+      </c>
+      <c r="C97" s="0">
+        <v>750.41426091137441</v>
+      </c>
+      <c r="D97" s="0">
+        <v>1039994.9581792068</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0">
+        <v>96</v>
+      </c>
+      <c r="B98" s="0">
+        <v>1398.0294147349621</v>
+      </c>
+      <c r="C98" s="0">
+        <v>746.42369241652477</v>
+      </c>
+      <c r="D98" s="0">
+        <v>1043522.2778533834</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0">
+        <v>97</v>
+      </c>
+      <c r="B99" s="0">
+        <v>1410.1112666318616</v>
+      </c>
+      <c r="C99" s="0">
+        <v>742.14951161802333</v>
+      </c>
+      <c r="D99" s="0">
+        <v>1046513.3878579083</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="0">
+        <v>98</v>
+      </c>
+      <c r="B100" s="0">
+        <v>1422.1348189787591</v>
+      </c>
+      <c r="C100" s="0">
+        <v>737.58766203101527</v>
+      </c>
+      <c r="D100" s="0">
+        <v>1048949.096223444</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0">
+        <v>99</v>
+      </c>
+      <c r="B101" s="0">
+        <v>1434.0947107893767</v>
+      </c>
+      <c r="C101" s="0">
+        <v>732.73369771155137</v>
+      </c>
+      <c r="D101" s="0">
+        <v>1050809.5203052778</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="0">
+        <v>100</v>
+      </c>
+      <c r="B102" s="0">
+        <v>1445.9853774056996</v>
+      </c>
+      <c r="C102" s="0">
+        <v>727.58272619971535</v>
+      </c>
+      <c r="D102" s="0">
+        <v>1052073.9829377632</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="0">
+        <v>101</v>
+      </c>
+      <c r="B103" s="0">
+        <v>1457.8010174166179</v>
+      </c>
+      <c r="C103" s="0">
+        <v>722.12934241106859</v>
+      </c>
+      <c r="D103" s="0">
+        <v>1052720.8900732491</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="0">
+        <v>102</v>
+      </c>
+      <c r="B104" s="0">
+        <v>1469.5355531096736</v>
+      </c>
+      <c r="C104" s="0">
+        <v>716.36755170849983</v>
+      </c>
+      <c r="D104" s="0">
+        <v>1052727.5863297731</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="0">
+        <v>103</v>
+      </c>
+      <c r="B105" s="0">
+        <v>1481.1825829991569</v>
+      </c>
+      <c r="C105" s="0">
+        <v>710.29067996875642</v>
+      </c>
+      <c r="D105" s="0">
+        <v>1052070.1840363501</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="0">
+        <v>104</v>
+      </c>
+      <c r="B106" s="0">
+        <v>1492.7353245864606</v>
+      </c>
+      <c r="C106" s="0">
+        <v>703.89126792277932</v>
+      </c>
+      <c r="D106" s="0">
+        <v>1050723.3602962853</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="0">
+        <v>105</v>
+      </c>
+      <c r="B107" s="0">
+        <v>1504.1865450010093</v>
+      </c>
+      <c r="C107" s="0">
+        <v>697.16094635783361</v>
+      </c>
+      <c r="D107" s="0">
+        <v>1048660.1152116237</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="0">
+        <v>106</v>
+      </c>
+      <c r="B108" s="0">
+        <v>1515.5284764986475</v>
+      </c>
+      <c r="C108" s="0">
+        <v>690.09028786879367</v>
+      </c>
+      <c r="D108" s="0">
+        <v>1045851.482620306</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="0">
+        <v>107</v>
+      </c>
+      <c r="B109" s="0">
+        <v>1526.752712897862</v>
+      </c>
+      <c r="C109" s="0">
+        <v>682.66862966105703</v>
+      </c>
+      <c r="D109" s="0">
+        <v>1042266.1823452847</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="0">
+        <v>108</v>
+      </c>
+      <c r="B110" s="0">
+        <v>1537.850081824648</v>
+      </c>
+      <c r="C110" s="0">
+        <v>674.88386033231859</v>
+      </c>
+      <c r="D110" s="0">
+        <v>1037870.1998341904</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="0">
+        <v>109</v>
+      </c>
+      <c r="B111" s="0">
+        <v>1548.8104859864652</v>
+      </c>
+      <c r="C111" s="0">
+        <v>666.72216144275603</v>
+      </c>
+      <c r="D111" s="0">
+        <v>1032626.2748821015</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="0">
+        <v>110</v>
+      </c>
+      <c r="B112" s="0">
+        <v>1559.6227044165041</v>
+      </c>
+      <c r="C112" s="0">
+        <v>658.16769180109384</v>
+      </c>
+      <c r="D112" s="0">
+        <v>1026493.2754463902</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0">
+        <v>111</v>
+      </c>
+      <c r="B113" s="0">
+        <v>1570.2741414397701</v>
+      </c>
+      <c r="C113" s="0">
+        <v>649.2021984192105</v>
+      </c>
+      <c r="D113" s="0">
+        <v>1019425.4247435371</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0">
+        <v>112</v>
+      </c>
+      <c r="B114" s="0">
+        <v>1580.7505065834107</v>
+      </c>
+      <c r="C114" s="0">
+        <v>639.80453252565565</v>
+      </c>
+      <c r="D114" s="0">
+        <v>1011371.3389042924</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="0">
+        <v>113</v>
+      </c>
+      <c r="B115" s="0">
+        <v>1591.0354021199423</v>
+      </c>
+      <c r="C115" s="0">
+        <v>629.95004111879121</v>
+      </c>
+      <c r="D115" s="0">
+        <v>1002272.8169869102</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="0">
+        <v>114</v>
+      </c>
+      <c r="B116" s="0">
+        <v>1601.1097853389965</v>
+      </c>
+      <c r="C116" s="0">
+        <v>619.60979309226627</v>
+      </c>
+      <c r="D116" s="0">
+        <v>992063.30281189852</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="0">
+        <v>115</v>
+      </c>
+      <c r="B117" s="0">
+        <v>1610.9512582816076</v>
+      </c>
+      <c r="C117" s="0">
+        <v>608.74958206735619</v>
+      </c>
+      <c r="D117" s="0">
+        <v>980665.90520981024</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="0">
+        <v>116</v>
+      </c>
+      <c r="B118" s="0">
+        <v>1620.5331156974048</v>
+      </c>
+      <c r="C118" s="0">
+        <v>597.32862257115949</v>
+      </c>
+      <c r="D118" s="0">
+        <v>967990.81383048021</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="0">
+        <v>117</v>
+      </c>
+      <c r="B119" s="0">
+        <v>1629.823047532718</v>
+      </c>
+      <c r="C119" s="0">
+        <v>585.2978167729035</v>
+      </c>
+      <c r="D119" s="0">
+        <v>953931.87144705991</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="0">
+        <v>118</v>
+      </c>
+      <c r="B120" s="0">
+        <v>1638.7813367235165</v>
+      </c>
+      <c r="C120" s="0">
+        <v>572.59740629651708</v>
+      </c>
+      <c r="D120" s="0">
+        <v>938361.94289502467</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="0">
+        <v>119</v>
+      </c>
+      <c r="B121" s="0">
+        <v>1647.3583006753381</v>
+      </c>
+      <c r="C121" s="0">
+        <v>559.15372071039133</v>
+      </c>
+      <c r="D121" s="0">
+        <v>921126.52316576289</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="0">
         <v>120</v>
       </c>
-      <c r="B26" s="0">
+      <c r="B122" s="0">
         <v>1655.4905653908636</v>
       </c>
-      <c r="C26" s="0">
+      <c r="C122" s="0">
         <v>544.87455903441446</v>
       </c>
-      <c r="D26" s="0">
+      <c r="D122" s="0">
         <v>902034.69180298026</v>
       </c>
     </row>
